--- a/research/traditional_assets/database/data/poland/poland_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_office_equipment_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08776078364862749</v>
+        <v>0.08763048815969511</v>
       </c>
       <c r="C2">
-        <v>2.251584994253379</v>
+        <v>2.233310201190026</v>
       </c>
       <c r="D2">
-        <v>2.10558499425338</v>
+        <v>2.110000201190026</v>
       </c>
       <c r="E2">
-        <v>-0.529</v>
+        <v>-0.50631</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02269</v>
       </c>
       <c r="G2">
         <v>0.146</v>
@@ -1445,28 +1445,28 @@
         <v>0.285</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001141307</v>
       </c>
       <c r="N2">
-        <v>0.285</v>
+        <v>0.283858693</v>
       </c>
       <c r="O2">
-        <v>0.05415</v>
+        <v>0.05393315167</v>
       </c>
       <c r="P2">
-        <v>0.23085</v>
+        <v>0.22992554133</v>
       </c>
       <c r="Q2">
-        <v>0.30085</v>
+        <v>0.29992554133</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08776078364862749</v>
+        <v>0.08810409915120718</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7748144325403289</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>249.7137054271988</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08763048815969511</v>
+        <v>0.0875001926707627</v>
       </c>
       <c r="C3">
-        <v>2.233310201190026</v>
+        <v>2.215053963554618</v>
       </c>
       <c r="D3">
-        <v>2.110000201190026</v>
+        <v>2.114433963554618</v>
       </c>
       <c r="E3">
-        <v>-0.50631</v>
+        <v>-0.48362</v>
       </c>
       <c r="F3">
-        <v>0.02269</v>
+        <v>0.04538</v>
       </c>
       <c r="G3">
         <v>0.146</v>
@@ -1527,28 +1527,28 @@
         <v>0.285</v>
       </c>
       <c r="M3">
-        <v>0.001141307</v>
+        <v>0.002282614</v>
       </c>
       <c r="N3">
-        <v>0.283858693</v>
+        <v>0.282717386</v>
       </c>
       <c r="O3">
-        <v>0.05393315167</v>
+        <v>0.05371630333999999</v>
       </c>
       <c r="P3">
-        <v>0.22992554133</v>
+        <v>0.22900108266</v>
       </c>
       <c r="Q3">
-        <v>0.29992554133</v>
+        <v>0.29900108266</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08810409915120718</v>
+        <v>0.088454421092615</v>
       </c>
       <c r="T3">
-        <v>0.7748144325403289</v>
+        <v>0.7812307019251975</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>249.7137054271988</v>
+        <v>124.8568527135994</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0875001926707627</v>
+        <v>0.0873698971818303</v>
       </c>
       <c r="C4">
-        <v>2.215053963554618</v>
+        <v>2.196816398565527</v>
       </c>
       <c r="D4">
-        <v>2.114433963554618</v>
+        <v>2.118886398565527</v>
       </c>
       <c r="E4">
-        <v>-0.48362</v>
+        <v>-0.46093</v>
       </c>
       <c r="F4">
-        <v>0.04538</v>
+        <v>0.06807000000000001</v>
       </c>
       <c r="G4">
         <v>0.146</v>
@@ -1609,28 +1609,28 @@
         <v>0.285</v>
       </c>
       <c r="M4">
-        <v>0.002282614</v>
+        <v>0.003423921</v>
       </c>
       <c r="N4">
-        <v>0.282717386</v>
+        <v>0.281576079</v>
       </c>
       <c r="O4">
-        <v>0.05371630333999999</v>
+        <v>0.05349945501</v>
       </c>
       <c r="P4">
-        <v>0.22900108266</v>
+        <v>0.22807662399</v>
       </c>
       <c r="Q4">
-        <v>0.29900108266</v>
+        <v>0.29807662399</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.088454421092615</v>
+        <v>0.08881196616683537</v>
       </c>
       <c r="T4">
-        <v>0.7812307019251975</v>
+        <v>0.7877792655241872</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>124.8568527135994</v>
+        <v>83.23790180906627</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0873698971818303</v>
+        <v>0.08723960169289792</v>
       </c>
       <c r="C5">
-        <v>2.196816398565527</v>
+        <v>2.178597624430534</v>
       </c>
       <c r="D5">
-        <v>2.118886398565527</v>
+        <v>2.123357624430534</v>
       </c>
       <c r="E5">
-        <v>-0.46093</v>
+        <v>-0.43824</v>
       </c>
       <c r="F5">
-        <v>0.06807000000000001</v>
+        <v>0.09076000000000001</v>
       </c>
       <c r="G5">
         <v>0.146</v>
@@ -1691,28 +1691,28 @@
         <v>0.285</v>
       </c>
       <c r="M5">
-        <v>0.003423921</v>
+        <v>0.004565228</v>
       </c>
       <c r="N5">
-        <v>0.281576079</v>
+        <v>0.280434772</v>
       </c>
       <c r="O5">
-        <v>0.05349945501</v>
+        <v>0.05328260668</v>
       </c>
       <c r="P5">
-        <v>0.22807662399</v>
+        <v>0.22715216532</v>
       </c>
       <c r="Q5">
-        <v>0.29807662399</v>
+        <v>0.29715216532</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08881196616683537</v>
+        <v>0.08917696009676866</v>
       </c>
       <c r="T5">
-        <v>0.7877792655241872</v>
+        <v>0.7944642575314891</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>83.23790180906627</v>
+        <v>62.4284263567997</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08723960169289792</v>
+        <v>0.08710930620396552</v>
       </c>
       <c r="C6">
-        <v>2.178597624430534</v>
+        <v>2.160397760357287</v>
       </c>
       <c r="D6">
-        <v>2.123357624430534</v>
+        <v>2.127847760357287</v>
       </c>
       <c r="E6">
-        <v>-0.43824</v>
+        <v>-0.41555</v>
       </c>
       <c r="F6">
-        <v>0.09076000000000001</v>
+        <v>0.11345</v>
       </c>
       <c r="G6">
         <v>0.146</v>
@@ -1773,28 +1773,28 @@
         <v>0.285</v>
       </c>
       <c r="M6">
-        <v>0.004565228</v>
+        <v>0.005706535</v>
       </c>
       <c r="N6">
-        <v>0.280434772</v>
+        <v>0.279293465</v>
       </c>
       <c r="O6">
-        <v>0.05328260668</v>
+        <v>0.05306575834999999</v>
       </c>
       <c r="P6">
-        <v>0.22715216532</v>
+        <v>0.22622770665</v>
       </c>
       <c r="Q6">
-        <v>0.29715216532</v>
+        <v>0.29622770665</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08917696009676866</v>
+        <v>0.08954963810943739</v>
       </c>
       <c r="T6">
-        <v>0.7944642575314891</v>
+        <v>0.8012899862126289</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.4284263567997</v>
+        <v>49.94274108543976</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08710930620396552</v>
+        <v>0.08697901071503314</v>
       </c>
       <c r="C7">
-        <v>2.160397760357287</v>
+        <v>2.142216926563895</v>
       </c>
       <c r="D7">
-        <v>2.127847760357287</v>
+        <v>2.132356926563895</v>
       </c>
       <c r="E7">
-        <v>-0.41555</v>
+        <v>-0.39286</v>
       </c>
       <c r="F7">
-        <v>0.11345</v>
+        <v>0.13614</v>
       </c>
       <c r="G7">
         <v>0.146</v>
@@ -1855,28 +1855,28 @@
         <v>0.285</v>
       </c>
       <c r="M7">
-        <v>0.005706535</v>
+        <v>0.006847842</v>
       </c>
       <c r="N7">
-        <v>0.279293465</v>
+        <v>0.278152158</v>
       </c>
       <c r="O7">
-        <v>0.05306575834999999</v>
+        <v>0.05284891002</v>
       </c>
       <c r="P7">
-        <v>0.22622770665</v>
+        <v>0.22530324798</v>
       </c>
       <c r="Q7">
-        <v>0.29622770665</v>
+        <v>0.29530324798</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08954963810943739</v>
+        <v>0.08993024544152461</v>
       </c>
       <c r="T7">
-        <v>0.8012899862126289</v>
+        <v>0.8082609431635803</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.94274108543976</v>
+        <v>41.61895090453314</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08697901071503314</v>
+        <v>0.08684871522610074</v>
       </c>
       <c r="C8">
-        <v>2.142216926563895</v>
+        <v>2.124055244289657</v>
       </c>
       <c r="D8">
-        <v>2.132356926563895</v>
+        <v>2.136885244289657</v>
       </c>
       <c r="E8">
-        <v>-0.39286</v>
+        <v>-0.37017</v>
       </c>
       <c r="F8">
-        <v>0.13614</v>
+        <v>0.15883</v>
       </c>
       <c r="G8">
         <v>0.146</v>
@@ -1937,28 +1937,28 @@
         <v>0.285</v>
       </c>
       <c r="M8">
-        <v>0.006847842</v>
+        <v>0.007989148999999999</v>
       </c>
       <c r="N8">
-        <v>0.278152158</v>
+        <v>0.277010851</v>
       </c>
       <c r="O8">
-        <v>0.05284891002</v>
+        <v>0.05263206169</v>
       </c>
       <c r="P8">
-        <v>0.22530324798</v>
+        <v>0.22437878931</v>
       </c>
       <c r="Q8">
-        <v>0.29530324798</v>
+        <v>0.29437878931</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08993024544152461</v>
+        <v>0.09031903787752768</v>
       </c>
       <c r="T8">
-        <v>0.8082609431635803</v>
+        <v>0.8153818131672405</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.61895090453314</v>
+        <v>35.67338648959984</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08684871522610074</v>
+        <v>0.08671841973716836</v>
       </c>
       <c r="C9">
-        <v>2.124055244289657</v>
+        <v>2.105912835805931</v>
       </c>
       <c r="D9">
-        <v>2.136885244289657</v>
+        <v>2.141432835805931</v>
       </c>
       <c r="E9">
-        <v>-0.37017</v>
+        <v>-0.34748</v>
       </c>
       <c r="F9">
-        <v>0.15883</v>
+        <v>0.18152</v>
       </c>
       <c r="G9">
         <v>0.146</v>
@@ -2019,28 +2019,28 @@
         <v>0.285</v>
       </c>
       <c r="M9">
-        <v>0.007989149000000001</v>
+        <v>0.009130456</v>
       </c>
       <c r="N9">
-        <v>0.277010851</v>
+        <v>0.275869544</v>
       </c>
       <c r="O9">
-        <v>0.05263206169</v>
+        <v>0.05241521336</v>
       </c>
       <c r="P9">
-        <v>0.22437878931</v>
+        <v>0.22345433064</v>
       </c>
       <c r="Q9">
-        <v>0.29437878931</v>
+        <v>0.29345433064</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09031903787752768</v>
+        <v>0.09071628232300907</v>
       </c>
       <c r="T9">
-        <v>0.8153818131672405</v>
+        <v>0.8226574846927192</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.67338648959983</v>
+        <v>31.21421317839985</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08671841973716836</v>
+        <v>0.08658812424823595</v>
       </c>
       <c r="C10">
-        <v>2.105912835805931</v>
+        <v>2.087789824427135</v>
       </c>
       <c r="D10">
-        <v>2.141432835805931</v>
+        <v>2.145999824427136</v>
       </c>
       <c r="E10">
-        <v>-0.34748</v>
+        <v>-0.32479</v>
       </c>
       <c r="F10">
-        <v>0.18152</v>
+        <v>0.20421</v>
       </c>
       <c r="G10">
         <v>0.146</v>
@@ -2101,28 +2101,28 @@
         <v>0.285</v>
       </c>
       <c r="M10">
-        <v>0.009130456</v>
+        <v>0.010271763</v>
       </c>
       <c r="N10">
-        <v>0.275869544</v>
+        <v>0.274728237</v>
       </c>
       <c r="O10">
-        <v>0.05241521336</v>
+        <v>0.05219836503</v>
       </c>
       <c r="P10">
-        <v>0.22345433064</v>
+        <v>0.22252987197</v>
       </c>
       <c r="Q10">
-        <v>0.29345433064</v>
+        <v>0.29252987197</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09071628232300907</v>
+        <v>0.09112225741564389</v>
       </c>
       <c r="T10">
-        <v>0.8226574846927192</v>
+        <v>0.8300930610868895</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.21421317839985</v>
+        <v>27.74596726968876</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08658812424823595</v>
+        <v>0.08645782875930356</v>
       </c>
       <c r="C11">
-        <v>2.087789824427135</v>
+        <v>2.069686334521897</v>
       </c>
       <c r="D11">
-        <v>2.145999824427136</v>
+        <v>2.150586334521897</v>
       </c>
       <c r="E11">
-        <v>-0.32479</v>
+        <v>-0.3021</v>
       </c>
       <c r="F11">
-        <v>0.20421</v>
+        <v>0.2269</v>
       </c>
       <c r="G11">
         <v>0.146</v>
@@ -2183,28 +2183,28 @@
         <v>0.285</v>
       </c>
       <c r="M11">
-        <v>0.010271763</v>
+        <v>0.01141307</v>
       </c>
       <c r="N11">
-        <v>0.274728237</v>
+        <v>0.27358693</v>
       </c>
       <c r="O11">
-        <v>0.05219836503</v>
+        <v>0.05198151669999999</v>
       </c>
       <c r="P11">
-        <v>0.22252987197</v>
+        <v>0.2216054132999999</v>
       </c>
       <c r="Q11">
-        <v>0.29252987197</v>
+        <v>0.2916054132999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09112225741564389</v>
+        <v>0.09153725417700395</v>
       </c>
       <c r="T11">
-        <v>0.8300930610868895</v>
+        <v>0.8376938725120417</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.74596726968876</v>
+        <v>24.97137054271988</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08645782875930356</v>
+        <v>0.08632753327037117</v>
       </c>
       <c r="C12">
-        <v>2.069686334521897</v>
+        <v>2.051602491524342</v>
       </c>
       <c r="D12">
-        <v>2.150586334521897</v>
+        <v>2.155192491524343</v>
       </c>
       <c r="E12">
-        <v>-0.3021</v>
+        <v>-0.27941</v>
       </c>
       <c r="F12">
-        <v>0.2269</v>
+        <v>0.24959</v>
       </c>
       <c r="G12">
         <v>0.146</v>
@@ -2265,28 +2265,28 @@
         <v>0.285</v>
       </c>
       <c r="M12">
-        <v>0.01141307</v>
+        <v>0.012554377</v>
       </c>
       <c r="N12">
-        <v>0.27358693</v>
+        <v>0.272445623</v>
       </c>
       <c r="O12">
-        <v>0.05198151669999999</v>
+        <v>0.05176466837</v>
       </c>
       <c r="P12">
-        <v>0.2216054132999999</v>
+        <v>0.22068095463</v>
       </c>
       <c r="Q12">
-        <v>0.2916054132999999</v>
+        <v>0.29068095463</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09153725417700395</v>
+        <v>0.09196157670828221</v>
       </c>
       <c r="T12">
-        <v>0.8376938725120417</v>
+        <v>0.8454654886883208</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.97137054271987</v>
+        <v>22.70124594792716</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08632753327037117</v>
+        <v>0.08619723778143877</v>
       </c>
       <c r="C13">
-        <v>2.051602491524342</v>
+        <v>2.03353842194553</v>
       </c>
       <c r="D13">
-        <v>2.155192491524343</v>
+        <v>2.15981842194553</v>
       </c>
       <c r="E13">
-        <v>-0.27941</v>
+        <v>-0.25672</v>
       </c>
       <c r="F13">
-        <v>0.24959</v>
+        <v>0.27228</v>
       </c>
       <c r="G13">
         <v>0.146</v>
@@ -2347,28 +2347,28 @@
         <v>0.285</v>
       </c>
       <c r="M13">
-        <v>0.012554377</v>
+        <v>0.013695684</v>
       </c>
       <c r="N13">
-        <v>0.272445623</v>
+        <v>0.271304316</v>
       </c>
       <c r="O13">
-        <v>0.05176466837</v>
+        <v>0.05154782004</v>
       </c>
       <c r="P13">
-        <v>0.22068095463</v>
+        <v>0.21975649596</v>
       </c>
       <c r="Q13">
-        <v>0.29068095463</v>
+        <v>0.28975649596</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09196157670828221</v>
+        <v>0.09239554293345315</v>
       </c>
       <c r="T13">
-        <v>0.8454654886883208</v>
+        <v>0.8534137325049699</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.70124594792716</v>
+        <v>20.80947545226657</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08619723778143877</v>
+        <v>0.08606694229250639</v>
       </c>
       <c r="C14">
-        <v>2.03353842194553</v>
+        <v>2.015494253385033</v>
       </c>
       <c r="D14">
-        <v>2.15981842194553</v>
+        <v>2.164464253385034</v>
       </c>
       <c r="E14">
-        <v>-0.25672</v>
+        <v>-0.23403</v>
       </c>
       <c r="F14">
-        <v>0.27228</v>
+        <v>0.29497</v>
       </c>
       <c r="G14">
         <v>0.146</v>
@@ -2429,28 +2429,28 @@
         <v>0.285</v>
       </c>
       <c r="M14">
-        <v>0.013695684</v>
+        <v>0.014836991</v>
       </c>
       <c r="N14">
-        <v>0.271304316</v>
+        <v>0.270163009</v>
       </c>
       <c r="O14">
-        <v>0.05154782004</v>
+        <v>0.05133097170999999</v>
       </c>
       <c r="P14">
-        <v>0.21975649596</v>
+        <v>0.2188320372899999</v>
       </c>
       <c r="Q14">
-        <v>0.28975649596</v>
+        <v>0.28883203729</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09239554293345315</v>
+        <v>0.0928394853936855</v>
       </c>
       <c r="T14">
-        <v>0.8534137325049699</v>
+        <v>0.8615446945702776</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.80947545226657</v>
+        <v>19.20874657132298</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08606694229250639</v>
+        <v>0.085936646803574</v>
       </c>
       <c r="C15">
-        <v>2.015494253385033</v>
+        <v>1.997470114542676</v>
       </c>
       <c r="D15">
-        <v>2.164464253385034</v>
+        <v>2.169130114542676</v>
       </c>
       <c r="E15">
-        <v>-0.23403</v>
+        <v>-0.21134</v>
       </c>
       <c r="F15">
-        <v>0.29497</v>
+        <v>0.3176600000000001</v>
       </c>
       <c r="G15">
         <v>0.146</v>
@@ -2511,28 +2511,28 @@
         <v>0.285</v>
       </c>
       <c r="M15">
-        <v>0.014836991</v>
+        <v>0.015978298</v>
       </c>
       <c r="N15">
-        <v>0.270163009</v>
+        <v>0.269021702</v>
       </c>
       <c r="O15">
-        <v>0.05133097170999999</v>
+        <v>0.05111412337999999</v>
       </c>
       <c r="P15">
-        <v>0.2188320372899999</v>
+        <v>0.21790757862</v>
       </c>
       <c r="Q15">
-        <v>0.28883203729</v>
+        <v>0.28790757862</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0928394853936855</v>
+        <v>0.09329375209717906</v>
       </c>
       <c r="T15">
-        <v>0.8615446945702776</v>
+        <v>0.869864748776639</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.20874657132298</v>
+        <v>17.83669324479991</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.085936646803574</v>
+        <v>0.08580635131464161</v>
       </c>
       <c r="C16">
-        <v>1.997470114542676</v>
+        <v>1.979466135230413</v>
       </c>
       <c r="D16">
-        <v>2.169130114542676</v>
+        <v>2.173816135230414</v>
       </c>
       <c r="E16">
-        <v>-0.21134</v>
+        <v>-0.1886499999999999</v>
       </c>
       <c r="F16">
-        <v>0.3176600000000001</v>
+        <v>0.3403500000000001</v>
       </c>
       <c r="G16">
         <v>0.146</v>
@@ -2593,28 +2593,28 @@
         <v>0.285</v>
       </c>
       <c r="M16">
-        <v>0.015978298</v>
+        <v>0.017119605</v>
       </c>
       <c r="N16">
-        <v>0.269021702</v>
+        <v>0.267880395</v>
       </c>
       <c r="O16">
-        <v>0.05111412337999999</v>
+        <v>0.05089727505</v>
       </c>
       <c r="P16">
-        <v>0.21790757862</v>
+        <v>0.21698311995</v>
       </c>
       <c r="Q16">
-        <v>0.28790757862</v>
+        <v>0.28698311995</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09329375209717906</v>
+        <v>0.09375870742899012</v>
       </c>
       <c r="T16">
-        <v>0.869864748776639</v>
+        <v>0.8783805689643266</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.83669324479991</v>
+        <v>16.64758036181325</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08580635131464161</v>
+        <v>0.08567605582570921</v>
       </c>
       <c r="C17">
-        <v>1.979466135230413</v>
+        <v>1.96148244638437</v>
       </c>
       <c r="D17">
-        <v>2.173816135230414</v>
+        <v>2.17852244638437</v>
       </c>
       <c r="E17">
-        <v>-0.18865</v>
+        <v>-0.16596</v>
       </c>
       <c r="F17">
-        <v>0.34035</v>
+        <v>0.36304</v>
       </c>
       <c r="G17">
         <v>0.146</v>
@@ -2675,28 +2675,28 @@
         <v>0.285</v>
       </c>
       <c r="M17">
-        <v>0.017119605</v>
+        <v>0.018260912</v>
       </c>
       <c r="N17">
-        <v>0.267880395</v>
+        <v>0.266739088</v>
       </c>
       <c r="O17">
-        <v>0.05089727505</v>
+        <v>0.05068042671999999</v>
       </c>
       <c r="P17">
-        <v>0.21698311995</v>
+        <v>0.21605866128</v>
       </c>
       <c r="Q17">
-        <v>0.28698311995</v>
+        <v>0.28605866128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09375870742899012</v>
+        <v>0.09423473312584429</v>
       </c>
       <c r="T17">
-        <v>0.8783805689643266</v>
+        <v>0.8870991467755305</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.64758036181325</v>
+        <v>15.60710658919992</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08567605582570921</v>
+        <v>0.08554576033677683</v>
       </c>
       <c r="C18">
-        <v>1.96148244638437</v>
+        <v>1.94351918007704</v>
       </c>
       <c r="D18">
-        <v>2.17852244638437</v>
+        <v>2.18324918007704</v>
       </c>
       <c r="E18">
-        <v>-0.16596</v>
+        <v>-0.14327</v>
       </c>
       <c r="F18">
-        <v>0.36304</v>
+        <v>0.3857300000000001</v>
       </c>
       <c r="G18">
         <v>0.146</v>
@@ -2757,28 +2757,28 @@
         <v>0.285</v>
       </c>
       <c r="M18">
-        <v>0.018260912</v>
+        <v>0.019402219</v>
       </c>
       <c r="N18">
-        <v>0.266739088</v>
+        <v>0.265597781</v>
       </c>
       <c r="O18">
-        <v>0.05068042671999999</v>
+        <v>0.05046357839</v>
       </c>
       <c r="P18">
-        <v>0.21605866128</v>
+        <v>0.21513420261</v>
       </c>
       <c r="Q18">
-        <v>0.28605866128</v>
+        <v>0.28513420261</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09423473312584429</v>
+        <v>0.09472222932141786</v>
       </c>
       <c r="T18">
-        <v>0.8870991467755305</v>
+        <v>0.8960278107990525</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.60710658919992</v>
+        <v>14.68904149571758</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08554576033677683</v>
+        <v>0.08541546484784442</v>
       </c>
       <c r="C19">
-        <v>1.94351918007704</v>
+        <v>1.925576469529639</v>
       </c>
       <c r="D19">
-        <v>2.18324918007704</v>
+        <v>2.187996469529639</v>
       </c>
       <c r="E19">
-        <v>-0.14327</v>
+        <v>-0.12058</v>
       </c>
       <c r="F19">
-        <v>0.3857300000000001</v>
+        <v>0.4084200000000001</v>
       </c>
       <c r="G19">
         <v>0.146</v>
@@ -2839,28 +2839,28 @@
         <v>0.285</v>
       </c>
       <c r="M19">
-        <v>0.019402219</v>
+        <v>0.020543526</v>
       </c>
       <c r="N19">
-        <v>0.265597781</v>
+        <v>0.264456474</v>
       </c>
       <c r="O19">
-        <v>0.05046357839</v>
+        <v>0.05024673006</v>
       </c>
       <c r="P19">
-        <v>0.21513420261</v>
+        <v>0.21420974394</v>
       </c>
       <c r="Q19">
-        <v>0.28513420261</v>
+        <v>0.28420974394</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09472222932141786</v>
+        <v>0.09522161566810294</v>
       </c>
       <c r="T19">
-        <v>0.8960278107990525</v>
+        <v>0.9051742471158311</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.68904149571758</v>
+        <v>13.87298363484438</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08541546484784443</v>
+        <v>0.08528516935891203</v>
       </c>
       <c r="C20">
-        <v>1.925576469529639</v>
+        <v>1.907654449124617</v>
       </c>
       <c r="D20">
-        <v>2.187996469529639</v>
+        <v>2.192764449124617</v>
       </c>
       <c r="E20">
-        <v>-0.12058</v>
+        <v>-0.09788999999999998</v>
       </c>
       <c r="F20">
-        <v>0.40842</v>
+        <v>0.43111</v>
       </c>
       <c r="G20">
         <v>0.146</v>
@@ -2921,28 +2921,28 @@
         <v>0.285</v>
       </c>
       <c r="M20">
-        <v>0.020543526</v>
+        <v>0.021684833</v>
       </c>
       <c r="N20">
-        <v>0.264456474</v>
+        <v>0.263315167</v>
       </c>
       <c r="O20">
-        <v>0.05024673006</v>
+        <v>0.05002988173</v>
       </c>
       <c r="P20">
-        <v>0.21420974394</v>
+        <v>0.21328528527</v>
       </c>
       <c r="Q20">
-        <v>0.28420974394</v>
+        <v>0.28328528527</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09522161566810294</v>
+        <v>0.09573333254186669</v>
       </c>
       <c r="T20">
-        <v>0.9051742471158311</v>
+        <v>0.9145465213663574</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.87298363484438</v>
+        <v>13.14282660143151</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08528516935891203</v>
+        <v>0.08539787386997966</v>
       </c>
       <c r="C21">
-        <v>1.907654449124617</v>
+        <v>1.880838975455885</v>
       </c>
       <c r="D21">
-        <v>2.192764449124617</v>
+        <v>2.188638975455885</v>
       </c>
       <c r="E21">
-        <v>-0.09788999999999998</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="F21">
-        <v>0.43111</v>
+        <v>0.4538</v>
       </c>
       <c r="G21">
         <v>0.146</v>
@@ -3003,45 +3003,45 @@
         <v>0.285</v>
       </c>
       <c r="M21">
-        <v>0.021684833</v>
+        <v>0.02350684</v>
       </c>
       <c r="N21">
-        <v>0.263315167</v>
+        <v>0.26149316</v>
       </c>
       <c r="O21">
-        <v>0.05002988173</v>
+        <v>0.0496837004</v>
       </c>
       <c r="P21">
-        <v>0.21328528527</v>
+        <v>0.2118094596</v>
       </c>
       <c r="Q21">
-        <v>0.28328528527</v>
+        <v>0.2818094596</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09573333254186669</v>
+        <v>0.09625784233747456</v>
       </c>
       <c r="T21">
-        <v>0.9145465213663574</v>
+        <v>0.924153102473147</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.19</v>
       </c>
       <c r="W21">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.14282660143151</v>
+        <v>12.12413067855994</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08539787386997966</v>
+        <v>0.08527972838104726</v>
       </c>
       <c r="C22">
-        <v>1.880838975455885</v>
+        <v>1.862474006072916</v>
       </c>
       <c r="D22">
-        <v>2.188638975455885</v>
+        <v>2.192964006072916</v>
       </c>
       <c r="E22">
-        <v>-0.07519999999999999</v>
+        <v>-0.05250999999999995</v>
       </c>
       <c r="F22">
-        <v>0.4538</v>
+        <v>0.4764900000000001</v>
       </c>
       <c r="G22">
         <v>0.146</v>
@@ -3085,28 +3085,28 @@
         <v>0.285</v>
       </c>
       <c r="M22">
-        <v>0.02350684</v>
+        <v>0.024682182</v>
       </c>
       <c r="N22">
-        <v>0.26149316</v>
+        <v>0.260317818</v>
       </c>
       <c r="O22">
-        <v>0.0496837004</v>
+        <v>0.04946038542</v>
       </c>
       <c r="P22">
-        <v>0.2118094596</v>
+        <v>0.21085743258</v>
       </c>
       <c r="Q22">
-        <v>0.2818094596</v>
+        <v>0.28085743258</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09625784233747456</v>
+        <v>0.09679563086208513</v>
       </c>
       <c r="T22">
-        <v>0.924153102473147</v>
+        <v>0.9340028881649185</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.12413067855994</v>
+        <v>11.54679112243804</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08527972838104726</v>
+        <v>0.08516158289211487</v>
       </c>
       <c r="C23">
-        <v>1.862474006072916</v>
+        <v>1.844126164163663</v>
       </c>
       <c r="D23">
-        <v>2.192964006072916</v>
+        <v>2.197306164163663</v>
       </c>
       <c r="E23">
-        <v>-0.05251</v>
+        <v>-0.02982000000000001</v>
       </c>
       <c r="F23">
-        <v>0.47649</v>
+        <v>0.49918</v>
       </c>
       <c r="G23">
         <v>0.146</v>
@@ -3167,28 +3167,28 @@
         <v>0.285</v>
       </c>
       <c r="M23">
-        <v>0.024682182</v>
+        <v>0.025857524</v>
       </c>
       <c r="N23">
-        <v>0.260317818</v>
+        <v>0.259142476</v>
       </c>
       <c r="O23">
-        <v>0.04946038542</v>
+        <v>0.04923707043999999</v>
       </c>
       <c r="P23">
-        <v>0.21085743258</v>
+        <v>0.20990540556</v>
       </c>
       <c r="Q23">
-        <v>0.28085743258</v>
+        <v>0.27990540556</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09679563086208513</v>
+        <v>0.0973472088360447</v>
       </c>
       <c r="T23">
-        <v>0.9340028881649185</v>
+        <v>0.9441052324641712</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.54679112243804</v>
+        <v>11.02193698050904</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08516158289211487</v>
+        <v>0.08504343740318246</v>
       </c>
       <c r="C24">
-        <v>1.844126164163663</v>
+        <v>1.825795551669261</v>
       </c>
       <c r="D24">
-        <v>2.197306164163663</v>
+        <v>2.201665551669261</v>
       </c>
       <c r="E24">
-        <v>-0.02982000000000001</v>
+        <v>-0.00712999999999997</v>
       </c>
       <c r="F24">
-        <v>0.49918</v>
+        <v>0.5218700000000001</v>
       </c>
       <c r="G24">
         <v>0.146</v>
@@ -3249,28 +3249,28 @@
         <v>0.285</v>
       </c>
       <c r="M24">
-        <v>0.025857524</v>
+        <v>0.027032866</v>
       </c>
       <c r="N24">
-        <v>0.259142476</v>
+        <v>0.257967134</v>
       </c>
       <c r="O24">
-        <v>0.04923707043999999</v>
+        <v>0.04901375546</v>
       </c>
       <c r="P24">
-        <v>0.20990540556</v>
+        <v>0.20895337854</v>
       </c>
       <c r="Q24">
-        <v>0.27990540556</v>
+        <v>0.27895337854</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0973472088360447</v>
+        <v>0.09791311351062658</v>
       </c>
       <c r="T24">
-        <v>0.9441052324641712</v>
+        <v>0.9544699753166513</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.02193698050904</v>
+        <v>10.54272232918256</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08504343740318246</v>
+        <v>0.08492529191425006</v>
       </c>
       <c r="C25">
-        <v>1.825795551669261</v>
+        <v>1.807482271341445</v>
       </c>
       <c r="D25">
-        <v>2.201665551669261</v>
+        <v>2.206042271341445</v>
       </c>
       <c r="E25">
-        <v>-0.00712999999999997</v>
+        <v>0.01556000000000002</v>
       </c>
       <c r="F25">
-        <v>0.5218700000000001</v>
+        <v>0.54456</v>
       </c>
       <c r="G25">
         <v>0.146</v>
@@ -3331,28 +3331,28 @@
         <v>0.285</v>
       </c>
       <c r="M25">
-        <v>0.027032866</v>
+        <v>0.028208208</v>
       </c>
       <c r="N25">
-        <v>0.257967134</v>
+        <v>0.256791792</v>
       </c>
       <c r="O25">
-        <v>0.04901375546</v>
+        <v>0.04879044048</v>
       </c>
       <c r="P25">
-        <v>0.20895337854</v>
+        <v>0.20800135152</v>
       </c>
       <c r="Q25">
-        <v>0.27895337854</v>
+        <v>0.2780013515199999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09791311351062658</v>
+        <v>0.09849391041348693</v>
       </c>
       <c r="T25">
-        <v>0.9544699753166513</v>
+        <v>0.9651074745599862</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.54272232918256</v>
+        <v>10.10344223213328</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08492529191425006</v>
+        <v>0.08515139642531769</v>
       </c>
       <c r="C26">
-        <v>1.807482271341445</v>
+        <v>1.776431349002553</v>
       </c>
       <c r="D26">
-        <v>2.206042271341445</v>
+        <v>2.197681349002553</v>
       </c>
       <c r="E26">
-        <v>0.01556000000000002</v>
+        <v>0.03825000000000001</v>
       </c>
       <c r="F26">
-        <v>0.54456</v>
+        <v>0.56725</v>
       </c>
       <c r="G26">
         <v>0.146</v>
@@ -3413,45 +3413,45 @@
         <v>0.285</v>
       </c>
       <c r="M26">
-        <v>0.028208208</v>
+        <v>0.030347875</v>
       </c>
       <c r="N26">
-        <v>0.256791792</v>
+        <v>0.254652125</v>
       </c>
       <c r="O26">
-        <v>0.04879044048</v>
+        <v>0.04838390374999999</v>
       </c>
       <c r="P26">
-        <v>0.20800135152</v>
+        <v>0.20626822125</v>
       </c>
       <c r="Q26">
-        <v>0.2780013515199999</v>
+        <v>0.2762682212499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09849391041348693</v>
+        <v>0.09909019523375691</v>
       </c>
       <c r="T26">
-        <v>0.9651074745599862</v>
+        <v>0.9760286404498101</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.10344223213328</v>
+        <v>9.391102342421009</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08515139642531769</v>
+        <v>0.08504702093638529</v>
       </c>
       <c r="C27">
-        <v>1.776431349002553</v>
+        <v>1.757593070423424</v>
       </c>
       <c r="D27">
-        <v>2.197681349002553</v>
+        <v>2.201533070423424</v>
       </c>
       <c r="E27">
-        <v>0.03825000000000001</v>
+        <v>0.06093999999999999</v>
       </c>
       <c r="F27">
-        <v>0.56725</v>
+        <v>0.58994</v>
       </c>
       <c r="G27">
         <v>0.146</v>
@@ -3495,28 +3495,28 @@
         <v>0.285</v>
       </c>
       <c r="M27">
-        <v>0.030347875</v>
+        <v>0.03156179</v>
       </c>
       <c r="N27">
-        <v>0.254652125</v>
+        <v>0.25343821</v>
       </c>
       <c r="O27">
-        <v>0.04838390374999999</v>
+        <v>0.0481532599</v>
       </c>
       <c r="P27">
-        <v>0.20626822125</v>
+        <v>0.2052849501</v>
       </c>
       <c r="Q27">
-        <v>0.2762682212499999</v>
+        <v>0.2752849501</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09909019523375691</v>
+        <v>0.09970259585998012</v>
       </c>
       <c r="T27">
-        <v>0.9760286404498101</v>
+        <v>0.9872449729853049</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.391102342421009</v>
+        <v>9.029906098481741</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08504702093638529</v>
+        <v>0.08494264544745289</v>
       </c>
       <c r="C28">
-        <v>1.757593070423424</v>
+        <v>1.738768316830663</v>
       </c>
       <c r="D28">
-        <v>2.201533070423424</v>
+        <v>2.205398316830664</v>
       </c>
       <c r="E28">
-        <v>0.06093999999999999</v>
+        <v>0.08363000000000009</v>
       </c>
       <c r="F28">
-        <v>0.58994</v>
+        <v>0.6126300000000001</v>
       </c>
       <c r="G28">
         <v>0.146</v>
@@ -3577,28 +3577,28 @@
         <v>0.285</v>
       </c>
       <c r="M28">
-        <v>0.03156179</v>
+        <v>0.03277570500000001</v>
       </c>
       <c r="N28">
-        <v>0.25343821</v>
+        <v>0.252224295</v>
       </c>
       <c r="O28">
-        <v>0.0481532599</v>
+        <v>0.04792261605</v>
       </c>
       <c r="P28">
-        <v>0.2052849501</v>
+        <v>0.20430167895</v>
       </c>
       <c r="Q28">
-        <v>0.2752849501</v>
+        <v>0.27430167895</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09970259585998012</v>
+        <v>0.1003317745855519</v>
       </c>
       <c r="T28">
-        <v>0.9872449729853049</v>
+        <v>0.9987686023025939</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.029906098481741</v>
+        <v>8.695465131871302</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08494264544745289</v>
+        <v>0.08483826995852049</v>
       </c>
       <c r="C29">
-        <v>1.738768316830663</v>
+        <v>1.719957159587293</v>
       </c>
       <c r="D29">
-        <v>2.205398316830664</v>
+        <v>2.209277159587293</v>
       </c>
       <c r="E29">
-        <v>0.08363000000000009</v>
+        <v>0.1063200000000001</v>
       </c>
       <c r="F29">
-        <v>0.6126300000000001</v>
+        <v>0.6353200000000001</v>
       </c>
       <c r="G29">
         <v>0.146</v>
@@ -3659,28 +3659,28 @@
         <v>0.285</v>
       </c>
       <c r="M29">
-        <v>0.03277570500000001</v>
+        <v>0.03398962000000001</v>
       </c>
       <c r="N29">
-        <v>0.252224295</v>
+        <v>0.25101038</v>
       </c>
       <c r="O29">
-        <v>0.04792261605</v>
+        <v>0.04769197219999999</v>
       </c>
       <c r="P29">
-        <v>0.20430167895</v>
+        <v>0.2033184078</v>
       </c>
       <c r="Q29">
-        <v>0.27430167895</v>
+        <v>0.2733184078</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1003317745855519</v>
+        <v>0.1009784304979451</v>
       </c>
       <c r="T29">
-        <v>0.9987686023025939</v>
+        <v>1.010612332434252</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.695465131871302</v>
+        <v>8.384912805733043</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08483826995852049</v>
+        <v>0.08473389446958812</v>
       </c>
       <c r="C30">
-        <v>1.719957159587293</v>
+        <v>1.701159670559268</v>
       </c>
       <c r="D30">
-        <v>2.209277159587293</v>
+        <v>2.213169670559268</v>
       </c>
       <c r="E30">
-        <v>0.1063200000000001</v>
+        <v>0.1290100000000001</v>
       </c>
       <c r="F30">
-        <v>0.6353200000000001</v>
+        <v>0.6580100000000001</v>
       </c>
       <c r="G30">
         <v>0.146</v>
@@ -3741,28 +3741,28 @@
         <v>0.285</v>
       </c>
       <c r="M30">
-        <v>0.03398962000000001</v>
+        <v>0.035203535</v>
       </c>
       <c r="N30">
-        <v>0.25101038</v>
+        <v>0.249796465</v>
       </c>
       <c r="O30">
-        <v>0.04769197219999999</v>
+        <v>0.04746132834999999</v>
       </c>
       <c r="P30">
-        <v>0.2033184078</v>
+        <v>0.20233513665</v>
       </c>
       <c r="Q30">
-        <v>0.2733184078</v>
+        <v>0.27233513665</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1009784304979451</v>
+        <v>0.1016433020698424</v>
       </c>
       <c r="T30">
-        <v>1.010612332434252</v>
+        <v>1.022789688766802</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.384912805733043</v>
+        <v>8.095777881397421</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08473389446958811</v>
+        <v>0.08462951898065571</v>
       </c>
       <c r="C31">
-        <v>1.701159670559268</v>
+        <v>1.682375922119922</v>
       </c>
       <c r="D31">
-        <v>2.213169670559268</v>
+        <v>2.217075922119922</v>
       </c>
       <c r="E31">
-        <v>0.12901</v>
+        <v>0.1516999999999999</v>
       </c>
       <c r="F31">
-        <v>0.65801</v>
+        <v>0.6807</v>
       </c>
       <c r="G31">
         <v>0.146</v>
@@ -3823,28 +3823,28 @@
         <v>0.285</v>
       </c>
       <c r="M31">
-        <v>0.035203535</v>
+        <v>0.03641745</v>
       </c>
       <c r="N31">
-        <v>0.249796465</v>
+        <v>0.24858255</v>
       </c>
       <c r="O31">
-        <v>0.04746132834999999</v>
+        <v>0.04723068449999999</v>
       </c>
       <c r="P31">
-        <v>0.20233513665</v>
+        <v>0.2013518655</v>
       </c>
       <c r="Q31">
-        <v>0.27233513665</v>
+        <v>0.2713518655</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1016433020698424</v>
+        <v>0.1023271699723653</v>
       </c>
       <c r="T31">
-        <v>1.022789688766802</v>
+        <v>1.035314969565996</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.095777881397421</v>
+        <v>7.825918618684175</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08462951898065571</v>
+        <v>0.08472602349172333</v>
       </c>
       <c r="C32">
-        <v>1.682375922119922</v>
+        <v>1.656073761893147</v>
       </c>
       <c r="D32">
-        <v>2.217075922119922</v>
+        <v>2.213463761893148</v>
       </c>
       <c r="E32">
-        <v>0.1516999999999999</v>
+        <v>0.17439</v>
       </c>
       <c r="F32">
-        <v>0.6807</v>
+        <v>0.7033900000000001</v>
       </c>
       <c r="G32">
         <v>0.146</v>
@@ -3905,45 +3905,45 @@
         <v>0.285</v>
       </c>
       <c r="M32">
-        <v>0.03641745</v>
+        <v>0.03819407700000001</v>
       </c>
       <c r="N32">
-        <v>0.24858255</v>
+        <v>0.246805923</v>
       </c>
       <c r="O32">
-        <v>0.04723068449999999</v>
+        <v>0.04689312537</v>
       </c>
       <c r="P32">
-        <v>0.2013518655</v>
+        <v>0.19991279763</v>
       </c>
       <c r="Q32">
-        <v>0.2713518655</v>
+        <v>0.26991279763</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1023271699723653</v>
+        <v>0.1030308601329324</v>
       </c>
       <c r="T32">
-        <v>1.035314969565996</v>
+        <v>1.048203301982559</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.825918618684175</v>
+        <v>7.461889967913086</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08472602349172333</v>
+        <v>0.08462812800279093</v>
       </c>
       <c r="C33">
-        <v>1.656073761893147</v>
+        <v>1.637048072559704</v>
       </c>
       <c r="D33">
-        <v>2.213463761893148</v>
+        <v>2.217128072559704</v>
       </c>
       <c r="E33">
-        <v>0.17439</v>
+        <v>0.19708</v>
       </c>
       <c r="F33">
-        <v>0.7033900000000001</v>
+        <v>0.7260800000000001</v>
       </c>
       <c r="G33">
         <v>0.146</v>
@@ -3987,28 +3987,28 @@
         <v>0.285</v>
       </c>
       <c r="M33">
-        <v>0.03819407700000001</v>
+        <v>0.039426144</v>
       </c>
       <c r="N33">
-        <v>0.246805923</v>
+        <v>0.245573856</v>
       </c>
       <c r="O33">
-        <v>0.04689312537</v>
+        <v>0.04665903263999999</v>
       </c>
       <c r="P33">
-        <v>0.19991279763</v>
+        <v>0.19891482336</v>
       </c>
       <c r="Q33">
-        <v>0.26991279763</v>
+        <v>0.26891482336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1030308601329324</v>
+        <v>0.1037552470629279</v>
       </c>
       <c r="T33">
-        <v>1.048203301982559</v>
+        <v>1.061470702999608</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.461889967913086</v>
+        <v>7.228705906415803</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08462812800279093</v>
+        <v>0.08453023251385855</v>
       </c>
       <c r="C34">
-        <v>1.637048072559704</v>
+        <v>1.618034535616517</v>
       </c>
       <c r="D34">
-        <v>2.217128072559704</v>
+        <v>2.220804535616517</v>
       </c>
       <c r="E34">
-        <v>0.19708</v>
+        <v>0.21977</v>
       </c>
       <c r="F34">
-        <v>0.7260800000000001</v>
+        <v>0.74877</v>
       </c>
       <c r="G34">
         <v>0.146</v>
@@ -4069,28 +4069,28 @@
         <v>0.285</v>
       </c>
       <c r="M34">
-        <v>0.039426144</v>
+        <v>0.04065821100000001</v>
       </c>
       <c r="N34">
-        <v>0.245573856</v>
+        <v>0.244341789</v>
       </c>
       <c r="O34">
-        <v>0.04665903263999999</v>
+        <v>0.04642493991</v>
       </c>
       <c r="P34">
-        <v>0.19891482336</v>
+        <v>0.19791684909</v>
       </c>
       <c r="Q34">
-        <v>0.26891482336</v>
+        <v>0.26791684909</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1037552470629279</v>
+        <v>0.104501257483371</v>
       </c>
       <c r="T34">
-        <v>1.061470702999608</v>
+        <v>1.075134145838062</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.228705906415803</v>
+        <v>7.00965421228199</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08453023251385855</v>
+        <v>0.08443233702492615</v>
       </c>
       <c r="C35">
-        <v>1.618034535616517</v>
+        <v>1.59903321161763</v>
       </c>
       <c r="D35">
-        <v>2.220804535616517</v>
+        <v>2.22449321161763</v>
       </c>
       <c r="E35">
-        <v>0.21977</v>
+        <v>0.2424600000000001</v>
       </c>
       <c r="F35">
-        <v>0.74877</v>
+        <v>0.7714600000000001</v>
       </c>
       <c r="G35">
         <v>0.146</v>
@@ -4151,28 +4151,28 @@
         <v>0.285</v>
       </c>
       <c r="M35">
-        <v>0.04065821100000001</v>
+        <v>0.04189027800000001</v>
       </c>
       <c r="N35">
-        <v>0.244341789</v>
+        <v>0.243109722</v>
       </c>
       <c r="O35">
-        <v>0.04642493991</v>
+        <v>0.04619084717999999</v>
       </c>
       <c r="P35">
-        <v>0.19791684909</v>
+        <v>0.19691887482</v>
       </c>
       <c r="Q35">
-        <v>0.26791684909</v>
+        <v>0.26691887482</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.104501257483371</v>
+        <v>0.1052698742801911</v>
       </c>
       <c r="T35">
-        <v>1.075134145838062</v>
+        <v>1.089211632398893</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.00965421228199</v>
+        <v>6.803487911920755</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08443233702492615</v>
+        <v>0.08433444153599375</v>
       </c>
       <c r="C36">
-        <v>1.59903321161763</v>
+        <v>1.580044161520066</v>
       </c>
       <c r="D36">
-        <v>2.22449321161763</v>
+        <v>2.228194161520066</v>
       </c>
       <c r="E36">
-        <v>0.2424600000000001</v>
+        <v>0.2651500000000001</v>
       </c>
       <c r="F36">
-        <v>0.7714600000000001</v>
+        <v>0.7941500000000001</v>
       </c>
       <c r="G36">
         <v>0.146</v>
@@ -4233,28 +4233,28 @@
         <v>0.285</v>
       </c>
       <c r="M36">
-        <v>0.04189027800000001</v>
+        <v>0.04312234500000001</v>
       </c>
       <c r="N36">
-        <v>0.243109722</v>
+        <v>0.241877655</v>
       </c>
       <c r="O36">
-        <v>0.04619084717999999</v>
+        <v>0.04595675445</v>
       </c>
       <c r="P36">
-        <v>0.19691887482</v>
+        <v>0.19592090055</v>
       </c>
       <c r="Q36">
-        <v>0.26691887482</v>
+        <v>0.26592090055</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1052698742801911</v>
+        <v>0.1060621408246058</v>
       </c>
       <c r="T36">
-        <v>1.089211632398893</v>
+        <v>1.103722272392365</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.803487911920755</v>
+        <v>6.609102543008733</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08433444153599375</v>
+        <v>0.08423654604706138</v>
       </c>
       <c r="C37">
-        <v>1.580044161520066</v>
+        <v>1.561067446687187</v>
       </c>
       <c r="D37">
-        <v>2.228194161520066</v>
+        <v>2.231907446687187</v>
       </c>
       <c r="E37">
-        <v>0.2651500000000001</v>
+        <v>0.2878400000000001</v>
       </c>
       <c r="F37">
-        <v>0.7941500000000001</v>
+        <v>0.8168400000000001</v>
       </c>
       <c r="G37">
         <v>0.146</v>
@@ -4315,28 +4315,28 @@
         <v>0.285</v>
       </c>
       <c r="M37">
-        <v>0.04312234500000001</v>
+        <v>0.04435441200000001</v>
       </c>
       <c r="N37">
-        <v>0.241877655</v>
+        <v>0.240645588</v>
       </c>
       <c r="O37">
-        <v>0.04595675445</v>
+        <v>0.04572266171999999</v>
       </c>
       <c r="P37">
-        <v>0.19592090055</v>
+        <v>0.19492292628</v>
       </c>
       <c r="Q37">
-        <v>0.26592090055</v>
+        <v>0.26492292628</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1060621408246058</v>
+        <v>0.1068791656985334</v>
       </c>
       <c r="T37">
-        <v>1.103722272392365</v>
+        <v>1.118686369885634</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.609102543008733</v>
+        <v>6.42551636125849</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08423654604706135</v>
+        <v>0.08413865055812897</v>
       </c>
       <c r="C38">
-        <v>1.561067446687189</v>
+        <v>1.542103128892089</v>
       </c>
       <c r="D38">
-        <v>2.231907446687189</v>
+        <v>2.235633128892089</v>
       </c>
       <c r="E38">
-        <v>0.28784</v>
+        <v>0.31053</v>
       </c>
       <c r="F38">
-        <v>0.81684</v>
+        <v>0.83953</v>
       </c>
       <c r="G38">
         <v>0.146</v>
@@ -4397,28 +4397,28 @@
         <v>0.285</v>
       </c>
       <c r="M38">
-        <v>0.044354412</v>
+        <v>0.045586479</v>
       </c>
       <c r="N38">
-        <v>0.240645588</v>
+        <v>0.239413521</v>
       </c>
       <c r="O38">
-        <v>0.04572266171999999</v>
+        <v>0.04548856898999999</v>
       </c>
       <c r="P38">
-        <v>0.19492292628</v>
+        <v>0.19392495201</v>
       </c>
       <c r="Q38">
-        <v>0.26492292628</v>
+        <v>0.26392495201</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1068791656985334</v>
+        <v>0.107722127870046</v>
       </c>
       <c r="T38">
-        <v>1.118686369885634</v>
+        <v>1.134125518092974</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.425516361258491</v>
+        <v>6.251853756900154</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08413865055812897</v>
+        <v>0.08434855506919658</v>
       </c>
       <c r="C39">
-        <v>1.542103128892089</v>
+        <v>1.511439838277181</v>
       </c>
       <c r="D39">
-        <v>2.235633128892089</v>
+        <v>2.227659838277181</v>
       </c>
       <c r="E39">
-        <v>0.31053</v>
+        <v>0.3332200000000001</v>
       </c>
       <c r="F39">
-        <v>0.83953</v>
+        <v>0.8622200000000001</v>
       </c>
       <c r="G39">
         <v>0.146</v>
@@ -4479,45 +4479,45 @@
         <v>0.285</v>
       </c>
       <c r="M39">
-        <v>0.045586479</v>
+        <v>0.04768076600000001</v>
       </c>
       <c r="N39">
-        <v>0.239413521</v>
+        <v>0.237319234</v>
       </c>
       <c r="O39">
-        <v>0.04548856898999999</v>
+        <v>0.04509065445999999</v>
       </c>
       <c r="P39">
-        <v>0.19392495201</v>
+        <v>0.19222857954</v>
       </c>
       <c r="Q39">
-        <v>0.26392495201</v>
+        <v>0.26222857954</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.107722127870046</v>
+        <v>0.1085922823696719</v>
       </c>
       <c r="T39">
-        <v>1.134125518092974</v>
+        <v>1.150062703339261</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.251853756900154</v>
+        <v>5.977252966112162</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08434855506919658</v>
+        <v>0.08425875958026419</v>
       </c>
       <c r="C40">
-        <v>1.511439838277181</v>
+        <v>1.492153777442253</v>
       </c>
       <c r="D40">
-        <v>2.227659838277181</v>
+        <v>2.231063777442253</v>
       </c>
       <c r="E40">
-        <v>0.3332200000000001</v>
+        <v>0.3559100000000001</v>
       </c>
       <c r="F40">
-        <v>0.8622200000000001</v>
+        <v>0.8849100000000001</v>
       </c>
       <c r="G40">
         <v>0.146</v>
@@ -4561,28 +4561,28 @@
         <v>0.285</v>
       </c>
       <c r="M40">
-        <v>0.04768076600000001</v>
+        <v>0.04893552300000001</v>
       </c>
       <c r="N40">
-        <v>0.237319234</v>
+        <v>0.236064477</v>
       </c>
       <c r="O40">
-        <v>0.04509065445999999</v>
+        <v>0.04485225062999999</v>
       </c>
       <c r="P40">
-        <v>0.19222857954</v>
+        <v>0.19121222637</v>
       </c>
       <c r="Q40">
-        <v>0.26222857954</v>
+        <v>0.26121222637</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1085922823696719</v>
+        <v>0.1094909665250233</v>
       </c>
       <c r="T40">
-        <v>1.150062703339261</v>
+        <v>1.16652241924936</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.977252966112162</v>
+        <v>5.823990069545183</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08425875958026419</v>
+        <v>0.0841689640913318</v>
       </c>
       <c r="C41">
-        <v>1.492153777442253</v>
+        <v>1.472878135194363</v>
       </c>
       <c r="D41">
-        <v>2.231063777442253</v>
+        <v>2.234478135194363</v>
       </c>
       <c r="E41">
-        <v>0.3559100000000001</v>
+        <v>0.3786</v>
       </c>
       <c r="F41">
-        <v>0.8849100000000001</v>
+        <v>0.9076000000000001</v>
       </c>
       <c r="G41">
         <v>0.146</v>
@@ -4643,28 +4643,28 @@
         <v>0.285</v>
       </c>
       <c r="M41">
-        <v>0.04893552300000001</v>
+        <v>0.05019028</v>
       </c>
       <c r="N41">
-        <v>0.236064477</v>
+        <v>0.23480972</v>
       </c>
       <c r="O41">
-        <v>0.04485225062999999</v>
+        <v>0.0446138468</v>
       </c>
       <c r="P41">
-        <v>0.19121222637</v>
+        <v>0.1901958732</v>
       </c>
       <c r="Q41">
-        <v>0.26121222637</v>
+        <v>0.2601958732</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1094909665250233</v>
+        <v>0.1104196068188863</v>
       </c>
       <c r="T41">
-        <v>1.16652241924936</v>
+        <v>1.183530792356463</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.823990069545183</v>
+        <v>5.678390317806555</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0841689640913318</v>
+        <v>0.0840791686023994</v>
       </c>
       <c r="C42">
-        <v>1.472878135194363</v>
+        <v>1.453612959439769</v>
       </c>
       <c r="D42">
-        <v>2.234478135194363</v>
+        <v>2.237902959439769</v>
       </c>
       <c r="E42">
-        <v>0.3786</v>
+        <v>0.4012900000000001</v>
       </c>
       <c r="F42">
-        <v>0.9076000000000001</v>
+        <v>0.9302900000000002</v>
       </c>
       <c r="G42">
         <v>0.146</v>
@@ -4725,28 +4725,28 @@
         <v>0.285</v>
       </c>
       <c r="M42">
-        <v>0.05019028</v>
+        <v>0.05144503700000001</v>
       </c>
       <c r="N42">
-        <v>0.23480972</v>
+        <v>0.2335549629999999</v>
       </c>
       <c r="O42">
-        <v>0.0446138468</v>
+        <v>0.04437544296999999</v>
       </c>
       <c r="P42">
-        <v>0.1901958732</v>
+        <v>0.18917952003</v>
       </c>
       <c r="Q42">
-        <v>0.2601958732</v>
+        <v>0.25917952003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1104196068188863</v>
+        <v>0.1113797264447448</v>
       </c>
       <c r="T42">
-        <v>1.183530792356463</v>
+        <v>1.201115720484145</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.678390317806555</v>
+        <v>5.539892992982003</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0840791686023994</v>
+        <v>0.08398937311346702</v>
       </c>
       <c r="C43">
-        <v>1.453612959439769</v>
+        <v>1.434358298378889</v>
       </c>
       <c r="D43">
-        <v>2.237902959439769</v>
+        <v>2.241338298378889</v>
       </c>
       <c r="E43">
-        <v>0.4012900000000001</v>
+        <v>0.4239800000000001</v>
       </c>
       <c r="F43">
-        <v>0.9302900000000002</v>
+        <v>0.9529800000000002</v>
       </c>
       <c r="G43">
         <v>0.146</v>
@@ -4807,28 +4807,28 @@
         <v>0.285</v>
       </c>
       <c r="M43">
-        <v>0.05144503700000001</v>
+        <v>0.05269979400000001</v>
       </c>
       <c r="N43">
-        <v>0.2335549629999999</v>
+        <v>0.232300206</v>
       </c>
       <c r="O43">
-        <v>0.04437544296999999</v>
+        <v>0.04413703913999999</v>
       </c>
       <c r="P43">
-        <v>0.18917952003</v>
+        <v>0.18816316686</v>
       </c>
       <c r="Q43">
-        <v>0.25917952003</v>
+        <v>0.25816316686</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1113797264447448</v>
+        <v>0.1123729536439086</v>
       </c>
       <c r="T43">
-        <v>1.201115720484145</v>
+        <v>1.219307025443817</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.539892992982003</v>
+        <v>5.407990778863384</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08398937311346703</v>
+        <v>0.08389957762453464</v>
       </c>
       <c r="C44">
-        <v>1.434358298378888</v>
+        <v>1.415114200508559</v>
       </c>
       <c r="D44">
-        <v>2.241338298378888</v>
+        <v>2.244784200508559</v>
       </c>
       <c r="E44">
-        <v>0.42398</v>
+        <v>0.44667</v>
       </c>
       <c r="F44">
-        <v>0.95298</v>
+        <v>0.97567</v>
       </c>
       <c r="G44">
         <v>0.146</v>
@@ -4889,28 +4889,28 @@
         <v>0.285</v>
       </c>
       <c r="M44">
-        <v>0.052699794</v>
+        <v>0.053954551</v>
       </c>
       <c r="N44">
-        <v>0.232300206</v>
+        <v>0.231045449</v>
       </c>
       <c r="O44">
-        <v>0.04413703913999999</v>
+        <v>0.04389863530999999</v>
       </c>
       <c r="P44">
-        <v>0.18816316686</v>
+        <v>0.18714681369</v>
       </c>
       <c r="Q44">
-        <v>0.25816316686</v>
+        <v>0.25714681369</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1123729536439086</v>
+        <v>0.1134010309202362</v>
       </c>
       <c r="T44">
-        <v>1.219307025443817</v>
+        <v>1.238136621805582</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.407990778863385</v>
+        <v>5.282223551447958</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08389957762453464</v>
+        <v>0.08380978213560225</v>
       </c>
       <c r="C45">
-        <v>1.415114200508559</v>
+        <v>1.395880714624316</v>
       </c>
       <c r="D45">
-        <v>2.244784200508559</v>
+        <v>2.248240714624316</v>
       </c>
       <c r="E45">
-        <v>0.44667</v>
+        <v>0.46936</v>
       </c>
       <c r="F45">
-        <v>0.97567</v>
+        <v>0.99836</v>
       </c>
       <c r="G45">
         <v>0.146</v>
@@ -4971,28 +4971,28 @@
         <v>0.285</v>
       </c>
       <c r="M45">
-        <v>0.053954551</v>
+        <v>0.05520930800000001</v>
       </c>
       <c r="N45">
-        <v>0.231045449</v>
+        <v>0.229790692</v>
       </c>
       <c r="O45">
-        <v>0.04389863530999999</v>
+        <v>0.04366023147999999</v>
       </c>
       <c r="P45">
-        <v>0.18714681369</v>
+        <v>0.18613046052</v>
       </c>
       <c r="Q45">
-        <v>0.25714681369</v>
+        <v>0.25613046052</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1134010309202362</v>
+        <v>0.1144658252421469</v>
       </c>
       <c r="T45">
-        <v>1.238136621805582</v>
+        <v>1.257638703751696</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.282223551447958</v>
+        <v>5.162173016187777</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08380978213560225</v>
+        <v>0.08371998664666984</v>
       </c>
       <c r="C46">
-        <v>1.395880714624316</v>
+        <v>1.376657889822704</v>
       </c>
       <c r="D46">
-        <v>2.248240714624316</v>
+        <v>2.251707889822705</v>
       </c>
       <c r="E46">
-        <v>0.46936</v>
+        <v>0.49205</v>
       </c>
       <c r="F46">
-        <v>0.99836</v>
+        <v>1.02105</v>
       </c>
       <c r="G46">
         <v>0.146</v>
@@ -5053,28 +5053,28 @@
         <v>0.285</v>
       </c>
       <c r="M46">
-        <v>0.05520930800000001</v>
+        <v>0.056464065</v>
       </c>
       <c r="N46">
-        <v>0.229790692</v>
+        <v>0.228535935</v>
       </c>
       <c r="O46">
-        <v>0.04366023147999999</v>
+        <v>0.04342182764999999</v>
       </c>
       <c r="P46">
-        <v>0.18613046052</v>
+        <v>0.18511410735</v>
       </c>
       <c r="Q46">
-        <v>0.25613046052</v>
+        <v>0.25511410735</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1144658252421469</v>
+        <v>0.1155693393575815</v>
       </c>
       <c r="T46">
-        <v>1.257638703751696</v>
+        <v>1.277849952314032</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.162173016187777</v>
+        <v>5.047458060272493</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08371998664666984</v>
+        <v>0.08363019115773745</v>
       </c>
       <c r="C47">
-        <v>1.376657889822704</v>
+        <v>1.357445775503593</v>
       </c>
       <c r="D47">
-        <v>2.251707889822705</v>
+        <v>2.255185775503593</v>
       </c>
       <c r="E47">
-        <v>0.49205</v>
+        <v>0.5147400000000001</v>
       </c>
       <c r="F47">
-        <v>1.02105</v>
+        <v>1.04374</v>
       </c>
       <c r="G47">
         <v>0.146</v>
@@ -5135,28 +5135,28 @@
         <v>0.285</v>
       </c>
       <c r="M47">
-        <v>0.056464065</v>
+        <v>0.05771882200000001</v>
       </c>
       <c r="N47">
-        <v>0.228535935</v>
+        <v>0.227281178</v>
       </c>
       <c r="O47">
-        <v>0.04342182764999999</v>
+        <v>0.04318342382</v>
       </c>
       <c r="P47">
-        <v>0.18511410735</v>
+        <v>0.18409775418</v>
       </c>
       <c r="Q47">
-        <v>0.25511410735</v>
+        <v>0.25409775418</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1155693393575815</v>
+        <v>0.1167137243661805</v>
       </c>
       <c r="T47">
-        <v>1.277849952314032</v>
+        <v>1.298809765637936</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.047458060272493</v>
+        <v>4.937730711136134</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08363019115773745</v>
+        <v>0.08354039566880507</v>
       </c>
       <c r="C48">
-        <v>1.357445775503593</v>
+        <v>1.338244421372528</v>
       </c>
       <c r="D48">
-        <v>2.255185775503593</v>
+        <v>2.258674421372528</v>
       </c>
       <c r="E48">
-        <v>0.5147400000000001</v>
+        <v>0.5374300000000002</v>
       </c>
       <c r="F48">
-        <v>1.04374</v>
+        <v>1.06643</v>
       </c>
       <c r="G48">
         <v>0.146</v>
@@ -5217,28 +5217,28 @@
         <v>0.285</v>
       </c>
       <c r="M48">
-        <v>0.05771882200000001</v>
+        <v>0.05897357900000001</v>
       </c>
       <c r="N48">
-        <v>0.227281178</v>
+        <v>0.226026421</v>
       </c>
       <c r="O48">
-        <v>0.04318342382</v>
+        <v>0.04294501999</v>
       </c>
       <c r="P48">
-        <v>0.18409775418</v>
+        <v>0.18308140101</v>
       </c>
       <c r="Q48">
-        <v>0.25409775418</v>
+        <v>0.25308140101</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1167137243661805</v>
+        <v>0.1179012937147265</v>
       </c>
       <c r="T48">
-        <v>1.298809765637936</v>
+        <v>1.320560515313686</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.937730711136134</v>
+        <v>4.832672610899195</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08354039566880507</v>
+        <v>0.08345060017987267</v>
       </c>
       <c r="C49">
-        <v>1.338244421372528</v>
+        <v>1.319053877443102</v>
       </c>
       <c r="D49">
-        <v>2.258674421372528</v>
+        <v>2.262173877443102</v>
       </c>
       <c r="E49">
-        <v>0.5374300000000002</v>
+        <v>0.5601200000000001</v>
       </c>
       <c r="F49">
-        <v>1.06643</v>
+        <v>1.08912</v>
       </c>
       <c r="G49">
         <v>0.146</v>
@@ -5299,28 +5299,28 @@
         <v>0.285</v>
       </c>
       <c r="M49">
-        <v>0.05897357900000001</v>
+        <v>0.06022833600000001</v>
       </c>
       <c r="N49">
-        <v>0.226026421</v>
+        <v>0.224771664</v>
       </c>
       <c r="O49">
-        <v>0.04294501999</v>
+        <v>0.04270661616</v>
       </c>
       <c r="P49">
-        <v>0.18308140101</v>
+        <v>0.18206504784</v>
       </c>
       <c r="Q49">
-        <v>0.25308140101</v>
+        <v>0.25206504784</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1179012937147265</v>
+        <v>0.1191345388074474</v>
       </c>
       <c r="T49">
-        <v>1.320560515313686</v>
+        <v>1.343147832284657</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.832672610899195</v>
+        <v>4.731991931505462</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08345060017987266</v>
+        <v>0.08336080469094027</v>
       </c>
       <c r="C50">
-        <v>1.319053877443103</v>
+        <v>1.299874194039336</v>
       </c>
       <c r="D50">
-        <v>2.262173877443103</v>
+        <v>2.265684194039336</v>
       </c>
       <c r="E50">
-        <v>0.5601200000000001</v>
+        <v>0.5828099999999999</v>
       </c>
       <c r="F50">
-        <v>1.08912</v>
+        <v>1.11181</v>
       </c>
       <c r="G50">
         <v>0.146</v>
@@ -5381,28 +5381,28 @@
         <v>0.285</v>
       </c>
       <c r="M50">
-        <v>0.06022833600000001</v>
+        <v>0.061483093</v>
       </c>
       <c r="N50">
-        <v>0.224771664</v>
+        <v>0.223516907</v>
       </c>
       <c r="O50">
-        <v>0.04270661616</v>
+        <v>0.04246821233</v>
       </c>
       <c r="P50">
-        <v>0.18206504784</v>
+        <v>0.18104869467</v>
       </c>
       <c r="Q50">
-        <v>0.25206504784</v>
+        <v>0.25104869467</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1191345388074474</v>
+        <v>0.1204161464528241</v>
       </c>
       <c r="T50">
-        <v>1.343147832284657</v>
+        <v>1.366620926391744</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.731991931505462</v>
+        <v>4.635420667597188</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08336080469094027</v>
+        <v>0.08327100920200788</v>
       </c>
       <c r="C51">
-        <v>1.299874194039336</v>
+        <v>1.2807054217981</v>
       </c>
       <c r="D51">
-        <v>2.265684194039336</v>
+        <v>2.2692054217981</v>
       </c>
       <c r="E51">
-        <v>0.5828099999999999</v>
+        <v>0.6055</v>
       </c>
       <c r="F51">
-        <v>1.11181</v>
+        <v>1.1345</v>
       </c>
       <c r="G51">
         <v>0.146</v>
@@ -5463,28 +5463,28 @@
         <v>0.285</v>
       </c>
       <c r="M51">
-        <v>0.061483093</v>
+        <v>0.06273785000000001</v>
       </c>
       <c r="N51">
-        <v>0.223516907</v>
+        <v>0.22226215</v>
       </c>
       <c r="O51">
-        <v>0.04246821233</v>
+        <v>0.04222980849999999</v>
       </c>
       <c r="P51">
-        <v>0.18104869467</v>
+        <v>0.1800323415</v>
       </c>
       <c r="Q51">
-        <v>0.25104869467</v>
+        <v>0.2500323415</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1204161464528241</v>
+        <v>0.1217490184040158</v>
       </c>
       <c r="T51">
-        <v>1.366620926391744</v>
+        <v>1.391032944263115</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.635420667597188</v>
+        <v>4.542712254245243</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08327100920200788</v>
+        <v>0.08421396371307549</v>
       </c>
       <c r="C52">
-        <v>1.2807054217981</v>
+        <v>1.221575777264447</v>
       </c>
       <c r="D52">
-        <v>2.2692054217981</v>
+        <v>2.232765777264447</v>
       </c>
       <c r="E52">
-        <v>0.6055</v>
+        <v>0.6281900000000001</v>
       </c>
       <c r="F52">
-        <v>1.1345</v>
+        <v>1.15719</v>
       </c>
       <c r="G52">
         <v>0.146</v>
@@ -5545,45 +5545,45 @@
         <v>0.285</v>
       </c>
       <c r="M52">
-        <v>0.06273785000000001</v>
+        <v>0.06688558200000001</v>
       </c>
       <c r="N52">
-        <v>0.22226215</v>
+        <v>0.218114418</v>
       </c>
       <c r="O52">
-        <v>0.04222980849999999</v>
+        <v>0.04144173942</v>
       </c>
       <c r="P52">
-        <v>0.1800323415</v>
+        <v>0.17667267858</v>
       </c>
       <c r="Q52">
-        <v>0.2500323415</v>
+        <v>0.24667267858</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1217490184040158</v>
+        <v>0.1231362932919908</v>
       </c>
       <c r="T52">
-        <v>1.391032944263115</v>
+        <v>1.416441371027195</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.542712254245243</v>
+        <v>4.261008000199504</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08421396371307549</v>
+        <v>0.08414441822414309</v>
       </c>
       <c r="C53">
-        <v>1.221575777264447</v>
+        <v>1.201533279698485</v>
       </c>
       <c r="D53">
-        <v>2.232765777264447</v>
+        <v>2.235413279698486</v>
       </c>
       <c r="E53">
-        <v>0.6281900000000001</v>
+        <v>0.65088</v>
       </c>
       <c r="F53">
-        <v>1.15719</v>
+        <v>1.17988</v>
       </c>
       <c r="G53">
         <v>0.146</v>
@@ -5627,28 +5627,28 @@
         <v>0.285</v>
       </c>
       <c r="M53">
-        <v>0.06688558200000001</v>
+        <v>0.068197064</v>
       </c>
       <c r="N53">
-        <v>0.218114418</v>
+        <v>0.216802936</v>
       </c>
       <c r="O53">
-        <v>0.04144173942</v>
+        <v>0.04119255784</v>
       </c>
       <c r="P53">
-        <v>0.17667267858</v>
+        <v>0.17561037816</v>
       </c>
       <c r="Q53">
-        <v>0.24667267858</v>
+        <v>0.24561037816</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1231362932919908</v>
+        <v>0.1245813713002981</v>
       </c>
       <c r="T53">
-        <v>1.416441371027195</v>
+        <v>1.442908482239778</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.261008000199504</v>
+        <v>4.179065538657206</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08414441822414309</v>
+        <v>0.08407487273521071</v>
       </c>
       <c r="C54">
-        <v>1.201533279698485</v>
+        <v>1.181497068139161</v>
       </c>
       <c r="D54">
-        <v>2.235413279698486</v>
+        <v>2.238067068139161</v>
       </c>
       <c r="E54">
-        <v>0.65088</v>
+        <v>0.6735700000000001</v>
       </c>
       <c r="F54">
-        <v>1.17988</v>
+        <v>1.20257</v>
       </c>
       <c r="G54">
         <v>0.146</v>
@@ -5709,28 +5709,28 @@
         <v>0.285</v>
       </c>
       <c r="M54">
-        <v>0.068197064</v>
+        <v>0.06950854600000002</v>
       </c>
       <c r="N54">
-        <v>0.216802936</v>
+        <v>0.215491454</v>
       </c>
       <c r="O54">
-        <v>0.04119255784</v>
+        <v>0.04094337626</v>
       </c>
       <c r="P54">
-        <v>0.17561037816</v>
+        <v>0.17454807774</v>
       </c>
       <c r="Q54">
-        <v>0.24561037816</v>
+        <v>0.24454807774</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1245813713002981</v>
+        <v>0.12608794198981</v>
       </c>
       <c r="T54">
-        <v>1.442908482239778</v>
+        <v>1.470501853503961</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.179065538657206</v>
+        <v>4.100215245474994</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08407487273521071</v>
+        <v>0.08400532724627831</v>
       </c>
       <c r="C55">
-        <v>1.181497068139161</v>
+        <v>1.161467165000528</v>
       </c>
       <c r="D55">
-        <v>2.238067068139161</v>
+        <v>2.240727165000528</v>
       </c>
       <c r="E55">
-        <v>0.6735700000000001</v>
+        <v>0.6962600000000002</v>
       </c>
       <c r="F55">
-        <v>1.20257</v>
+        <v>1.22526</v>
       </c>
       <c r="G55">
         <v>0.146</v>
@@ -5791,28 +5791,28 @@
         <v>0.285</v>
       </c>
       <c r="M55">
-        <v>0.06950854600000002</v>
+        <v>0.07082002800000002</v>
       </c>
       <c r="N55">
-        <v>0.215491454</v>
+        <v>0.2141799719999999</v>
       </c>
       <c r="O55">
-        <v>0.04094337626</v>
+        <v>0.04069419467999999</v>
       </c>
       <c r="P55">
-        <v>0.17454807774</v>
+        <v>0.17348577732</v>
       </c>
       <c r="Q55">
-        <v>0.24454807774</v>
+        <v>0.24348577732</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.12608794198981</v>
+        <v>0.1276600157527789</v>
       </c>
       <c r="T55">
-        <v>1.470501853503961</v>
+        <v>1.499294936562238</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.100215245474994</v>
+        <v>4.024285333521753</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08400532724627831</v>
+        <v>0.08549503175734592</v>
       </c>
       <c r="C56">
-        <v>1.161467165000528</v>
+        <v>1.083145014507073</v>
       </c>
       <c r="D56">
-        <v>2.240727165000528</v>
+        <v>2.185095014507073</v>
       </c>
       <c r="E56">
-        <v>0.6962600000000002</v>
+        <v>0.7189500000000001</v>
       </c>
       <c r="F56">
-        <v>1.22526</v>
+        <v>1.24795</v>
       </c>
       <c r="G56">
         <v>0.146</v>
@@ -5873,45 +5873,45 @@
         <v>0.285</v>
       </c>
       <c r="M56">
-        <v>0.07082002800000002</v>
+        <v>0.076499335</v>
       </c>
       <c r="N56">
-        <v>0.2141799719999999</v>
+        <v>0.208500665</v>
       </c>
       <c r="O56">
-        <v>0.04069419467999999</v>
+        <v>0.03961512634999999</v>
       </c>
       <c r="P56">
-        <v>0.17348577732</v>
+        <v>0.16888553865</v>
       </c>
       <c r="Q56">
-        <v>0.24348577732</v>
+        <v>0.23888553865</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1276600157527789</v>
+        <v>0.1293019594607687</v>
       </c>
       <c r="T56">
-        <v>1.499294936562238</v>
+        <v>1.529367712200884</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.024285333521753</v>
+        <v>3.725522581340086</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08549503175734592</v>
+        <v>0.08545383626841352</v>
       </c>
       <c r="C57">
-        <v>1.083145014507073</v>
+        <v>1.061956271353174</v>
       </c>
       <c r="D57">
-        <v>2.185095014507073</v>
+        <v>2.186596271353175</v>
       </c>
       <c r="E57">
-        <v>0.7189500000000001</v>
+        <v>0.7416400000000002</v>
       </c>
       <c r="F57">
-        <v>1.24795</v>
+        <v>1.27064</v>
       </c>
       <c r="G57">
         <v>0.146</v>
@@ -5955,28 +5955,28 @@
         <v>0.285</v>
       </c>
       <c r="M57">
-        <v>0.076499335</v>
+        <v>0.07789023200000002</v>
       </c>
       <c r="N57">
-        <v>0.208500665</v>
+        <v>0.207109768</v>
       </c>
       <c r="O57">
-        <v>0.03961512634999999</v>
+        <v>0.03935085592</v>
       </c>
       <c r="P57">
-        <v>0.16888553865</v>
+        <v>0.16775891208</v>
       </c>
       <c r="Q57">
-        <v>0.23888553865</v>
+        <v>0.23775891208</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1293019594607687</v>
+        <v>0.1310185369736671</v>
       </c>
       <c r="T57">
-        <v>1.529367712200884</v>
+        <v>1.56080743218674</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.725522581340086</v>
+        <v>3.658995392387584</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08545383626841352</v>
+        <v>0.08541264077948113</v>
       </c>
       <c r="C58">
-        <v>1.061956271353174</v>
+        <v>1.04076959247713</v>
       </c>
       <c r="D58">
-        <v>2.186596271353175</v>
+        <v>2.18809959247713</v>
       </c>
       <c r="E58">
-        <v>0.7416400000000002</v>
+        <v>0.7643300000000003</v>
       </c>
       <c r="F58">
-        <v>1.27064</v>
+        <v>1.29333</v>
       </c>
       <c r="G58">
         <v>0.146</v>
@@ -6037,28 +6037,28 @@
         <v>0.285</v>
       </c>
       <c r="M58">
-        <v>0.07789023200000002</v>
+        <v>0.07928112900000002</v>
       </c>
       <c r="N58">
-        <v>0.207109768</v>
+        <v>0.205718871</v>
       </c>
       <c r="O58">
-        <v>0.03935085592</v>
+        <v>0.03908658548999999</v>
       </c>
       <c r="P58">
-        <v>0.16775891208</v>
+        <v>0.16663228551</v>
       </c>
       <c r="Q58">
-        <v>0.23775891208</v>
+        <v>0.23663228551</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1310185369736671</v>
+        <v>0.1328149553011189</v>
       </c>
       <c r="T58">
-        <v>1.56080743218674</v>
+        <v>1.593709464730078</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.658995392387584</v>
+        <v>3.594802490766749</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08541264077948113</v>
+        <v>0.08537144529054874</v>
       </c>
       <c r="C59">
-        <v>1.04076959247713</v>
+        <v>1.019584982139544</v>
       </c>
       <c r="D59">
-        <v>2.18809959247713</v>
+        <v>2.189604982139544</v>
       </c>
       <c r="E59">
-        <v>0.7643300000000003</v>
+        <v>0.7870200000000002</v>
       </c>
       <c r="F59">
-        <v>1.29333</v>
+        <v>1.31602</v>
       </c>
       <c r="G59">
         <v>0.146</v>
@@ -6119,28 +6119,28 @@
         <v>0.285</v>
       </c>
       <c r="M59">
-        <v>0.07928112900000002</v>
+        <v>0.08067202600000001</v>
       </c>
       <c r="N59">
-        <v>0.205718871</v>
+        <v>0.204327974</v>
       </c>
       <c r="O59">
-        <v>0.03908658548999999</v>
+        <v>0.03882231505999999</v>
       </c>
       <c r="P59">
-        <v>0.16663228551</v>
+        <v>0.16550565894</v>
       </c>
       <c r="Q59">
-        <v>0.23663228551</v>
+        <v>0.23550565894</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1328149553011189</v>
+        <v>0.1346969173584494</v>
       </c>
       <c r="T59">
-        <v>1.593709464730078</v>
+        <v>1.628178260727861</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.594802490766749</v>
+        <v>3.532823137477667</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08537144529054873</v>
+        <v>0.08666836980161635</v>
       </c>
       <c r="C60">
-        <v>1.019584982139544</v>
+        <v>0.9504748354669574</v>
       </c>
       <c r="D60">
-        <v>2.189604982139544</v>
+        <v>2.143184835466958</v>
       </c>
       <c r="E60">
-        <v>0.7870199999999999</v>
+        <v>0.80971</v>
       </c>
       <c r="F60">
-        <v>1.31602</v>
+        <v>1.33871</v>
       </c>
       <c r="G60">
         <v>0.146</v>
@@ -6201,45 +6201,45 @@
         <v>0.285</v>
       </c>
       <c r="M60">
-        <v>0.08067202599999999</v>
+        <v>0.08581131100000002</v>
       </c>
       <c r="N60">
-        <v>0.204327974</v>
+        <v>0.199188689</v>
       </c>
       <c r="O60">
-        <v>0.03882231505999999</v>
+        <v>0.03784585090999999</v>
       </c>
       <c r="P60">
-        <v>0.16550565894</v>
+        <v>0.16134283809</v>
       </c>
       <c r="Q60">
-        <v>0.23550565894</v>
+        <v>0.23134283809</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1346969173584494</v>
+        <v>0.1366706824429667</v>
       </c>
       <c r="T60">
-        <v>1.628178260727861</v>
+        <v>1.664328461408462</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.19</v>
       </c>
       <c r="W60">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.532823137477668</v>
+        <v>3.321240483087363</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08666836980161635</v>
+        <v>0.08664985431268396</v>
       </c>
       <c r="C61">
-        <v>0.9504748354669574</v>
+        <v>0.9284336974288803</v>
       </c>
       <c r="D61">
-        <v>2.143184835466958</v>
+        <v>2.14383369742888</v>
       </c>
       <c r="E61">
-        <v>0.80971</v>
+        <v>0.8323999999999999</v>
       </c>
       <c r="F61">
-        <v>1.33871</v>
+        <v>1.3614</v>
       </c>
       <c r="G61">
         <v>0.146</v>
@@ -6283,28 +6283,28 @@
         <v>0.285</v>
       </c>
       <c r="M61">
-        <v>0.08581131100000002</v>
+        <v>0.08726574000000001</v>
       </c>
       <c r="N61">
-        <v>0.199188689</v>
+        <v>0.19773426</v>
       </c>
       <c r="O61">
-        <v>0.03784585090999999</v>
+        <v>0.03756950939999999</v>
       </c>
       <c r="P61">
-        <v>0.16134283809</v>
+        <v>0.1601647506</v>
       </c>
       <c r="Q61">
-        <v>0.23134283809</v>
+        <v>0.2301647506</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1366706824429667</v>
+        <v>0.1387431357817099</v>
       </c>
       <c r="T61">
-        <v>1.664328461408462</v>
+        <v>1.702286172123094</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.321240483087363</v>
+        <v>3.265886475035907</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08664985431268396</v>
+        <v>0.08663133882375157</v>
       </c>
       <c r="C62">
-        <v>0.9284336974288803</v>
+        <v>0.9063929524034302</v>
       </c>
       <c r="D62">
-        <v>2.14383369742888</v>
+        <v>2.14448295240343</v>
       </c>
       <c r="E62">
-        <v>0.8323999999999999</v>
+        <v>0.85509</v>
       </c>
       <c r="F62">
-        <v>1.3614</v>
+        <v>1.38409</v>
       </c>
       <c r="G62">
         <v>0.146</v>
@@ -6365,28 +6365,28 @@
         <v>0.285</v>
       </c>
       <c r="M62">
-        <v>0.08726574000000001</v>
+        <v>0.08872016900000002</v>
       </c>
       <c r="N62">
-        <v>0.19773426</v>
+        <v>0.196279831</v>
       </c>
       <c r="O62">
-        <v>0.03756950939999999</v>
+        <v>0.03729316788999999</v>
       </c>
       <c r="P62">
-        <v>0.1601647506</v>
+        <v>0.15898666311</v>
       </c>
       <c r="Q62">
-        <v>0.2301647506</v>
+        <v>0.22898666311</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1387431357817099</v>
+        <v>0.1409218687788502</v>
       </c>
       <c r="T62">
-        <v>1.702286172123094</v>
+        <v>1.742190432105143</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.265886475035907</v>
+        <v>3.212347352494334</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08663133882375157</v>
+        <v>0.08661282333481918</v>
       </c>
       <c r="C63">
-        <v>0.9063929524034302</v>
+        <v>0.8843526007477835</v>
       </c>
       <c r="D63">
-        <v>2.14448295240343</v>
+        <v>2.145132600747784</v>
       </c>
       <c r="E63">
-        <v>0.85509</v>
+        <v>0.8777800000000001</v>
       </c>
       <c r="F63">
-        <v>1.38409</v>
+        <v>1.40678</v>
       </c>
       <c r="G63">
         <v>0.146</v>
@@ -6447,28 +6447,28 @@
         <v>0.285</v>
       </c>
       <c r="M63">
-        <v>0.08872016900000002</v>
+        <v>0.09017459800000001</v>
       </c>
       <c r="N63">
-        <v>0.196279831</v>
+        <v>0.194825402</v>
       </c>
       <c r="O63">
-        <v>0.03729316788999999</v>
+        <v>0.03701682638</v>
       </c>
       <c r="P63">
-        <v>0.15898666311</v>
+        <v>0.15780857562</v>
       </c>
       <c r="Q63">
-        <v>0.22898666311</v>
+        <v>0.22780857562</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1409218687788502</v>
+        <v>0.1432152719337347</v>
       </c>
       <c r="T63">
-        <v>1.742190432105143</v>
+        <v>1.784194916296773</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.212347352494334</v>
+        <v>3.160535298421846</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08661282333481918</v>
+        <v>0.08659430784588679</v>
       </c>
       <c r="C64">
-        <v>0.8843526007477835</v>
+        <v>0.8623126428195518</v>
       </c>
       <c r="D64">
-        <v>2.145132600747784</v>
+        <v>2.145782642819552</v>
       </c>
       <c r="E64">
-        <v>0.8777800000000001</v>
+        <v>0.90047</v>
       </c>
       <c r="F64">
-        <v>1.40678</v>
+        <v>1.42947</v>
       </c>
       <c r="G64">
         <v>0.146</v>
@@ -6529,28 +6529,28 @@
         <v>0.285</v>
       </c>
       <c r="M64">
-        <v>0.09017459800000001</v>
+        <v>0.091629027</v>
       </c>
       <c r="N64">
-        <v>0.194825402</v>
+        <v>0.193370973</v>
       </c>
       <c r="O64">
-        <v>0.03701682638</v>
+        <v>0.03674048486999999</v>
       </c>
       <c r="P64">
-        <v>0.15780857562</v>
+        <v>0.15663048813</v>
       </c>
       <c r="Q64">
-        <v>0.22780857562</v>
+        <v>0.22663048813</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1432152719337347</v>
+        <v>0.145632642826721</v>
       </c>
       <c r="T64">
-        <v>1.784194916296773</v>
+        <v>1.82846991314741</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.160535298421846</v>
+        <v>3.110368071462769</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08659430784588679</v>
+        <v>0.0865757923569544</v>
       </c>
       <c r="C65">
-        <v>0.8623126428195518</v>
+        <v>0.8402730789767769</v>
       </c>
       <c r="D65">
-        <v>2.145782642819552</v>
+        <v>2.146433078976777</v>
       </c>
       <c r="E65">
-        <v>0.90047</v>
+        <v>0.9231600000000001</v>
       </c>
       <c r="F65">
-        <v>1.42947</v>
+        <v>1.45216</v>
       </c>
       <c r="G65">
         <v>0.146</v>
@@ -6611,28 +6611,28 @@
         <v>0.285</v>
       </c>
       <c r="M65">
-        <v>0.091629027</v>
+        <v>0.09308345600000001</v>
       </c>
       <c r="N65">
-        <v>0.193370973</v>
+        <v>0.191916544</v>
       </c>
       <c r="O65">
-        <v>0.03674048486999999</v>
+        <v>0.03646414335999999</v>
       </c>
       <c r="P65">
-        <v>0.15663048813</v>
+        <v>0.15545240064</v>
       </c>
       <c r="Q65">
-        <v>0.22663048813</v>
+        <v>0.22545240064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.145632642826721</v>
+        <v>0.1481843121026511</v>
       </c>
       <c r="T65">
-        <v>1.82846991314741</v>
+        <v>1.875204632045305</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.110368071462769</v>
+        <v>3.061768570346163</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0865757923569544</v>
+        <v>0.086557276868022</v>
       </c>
       <c r="C66">
-        <v>0.8402730789767769</v>
+        <v>0.8182339095779374</v>
       </c>
       <c r="D66">
-        <v>2.146433078976777</v>
+        <v>2.147083909577938</v>
       </c>
       <c r="E66">
-        <v>0.9231600000000001</v>
+        <v>0.9458500000000002</v>
       </c>
       <c r="F66">
-        <v>1.45216</v>
+        <v>1.47485</v>
       </c>
       <c r="G66">
         <v>0.146</v>
@@ -6693,28 +6693,28 @@
         <v>0.285</v>
       </c>
       <c r="M66">
-        <v>0.09308345600000001</v>
+        <v>0.09453788500000002</v>
       </c>
       <c r="N66">
-        <v>0.191916544</v>
+        <v>0.190462115</v>
       </c>
       <c r="O66">
-        <v>0.03646414335999999</v>
+        <v>0.03618780184999999</v>
       </c>
       <c r="P66">
-        <v>0.15545240064</v>
+        <v>0.15427431315</v>
       </c>
       <c r="Q66">
-        <v>0.22545240064</v>
+        <v>0.22427431315</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1481843121026511</v>
+        <v>0.1508817910514914</v>
       </c>
       <c r="T66">
-        <v>1.875204632045305</v>
+        <v>1.924609906308793</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.061768570346163</v>
+        <v>3.014664438494683</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.086557276868022</v>
+        <v>0.0907086413790896</v>
       </c>
       <c r="C67">
-        <v>0.8182339095779374</v>
+        <v>0.658868434207766</v>
       </c>
       <c r="D67">
-        <v>2.147083909577938</v>
+        <v>2.010408434207766</v>
       </c>
       <c r="E67">
-        <v>0.9458500000000002</v>
+        <v>0.9685400000000001</v>
       </c>
       <c r="F67">
-        <v>1.47485</v>
+        <v>1.49754</v>
       </c>
       <c r="G67">
         <v>0.146</v>
@@ -6775,45 +6775,45 @@
         <v>0.285</v>
       </c>
       <c r="M67">
-        <v>0.09453788500000002</v>
+        <v>0.107673126</v>
       </c>
       <c r="N67">
-        <v>0.190462115</v>
+        <v>0.177326874</v>
       </c>
       <c r="O67">
-        <v>0.03618780184999999</v>
+        <v>0.03369210606</v>
       </c>
       <c r="P67">
-        <v>0.15427431315</v>
+        <v>0.14363476794</v>
       </c>
       <c r="Q67">
-        <v>0.22427431315</v>
+        <v>0.21363476794</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1508817910514914</v>
+        <v>0.1537379452326165</v>
       </c>
       <c r="T67">
-        <v>1.924609906308793</v>
+        <v>1.976921373176017</v>
       </c>
       <c r="U67">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.19</v>
       </c>
       <c r="W67">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.014664438494683</v>
+        <v>2.64690002591733</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0907086413790896</v>
+        <v>0.09075330589015722</v>
       </c>
       <c r="C68">
-        <v>0.658868434207766</v>
+        <v>0.6348024918124833</v>
       </c>
       <c r="D68">
-        <v>2.010408434207766</v>
+        <v>2.009032491812484</v>
       </c>
       <c r="E68">
-        <v>0.9685400000000001</v>
+        <v>0.9912300000000002</v>
       </c>
       <c r="F68">
-        <v>1.49754</v>
+        <v>1.52023</v>
       </c>
       <c r="G68">
         <v>0.146</v>
@@ -6857,28 +6857,28 @@
         <v>0.285</v>
       </c>
       <c r="M68">
-        <v>0.107673126</v>
+        <v>0.109304537</v>
       </c>
       <c r="N68">
-        <v>0.177326874</v>
+        <v>0.1756954629999999</v>
       </c>
       <c r="O68">
-        <v>0.03369210606</v>
+        <v>0.03338213796999999</v>
       </c>
       <c r="P68">
-        <v>0.14363476794</v>
+        <v>0.1423133250299999</v>
       </c>
       <c r="Q68">
-        <v>0.21363476794</v>
+        <v>0.2123133250299999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1537379452326165</v>
+        <v>0.1567671996671431</v>
       </c>
       <c r="T68">
-        <v>1.976921373176017</v>
+        <v>2.032403231974587</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.64690002591733</v>
+        <v>2.60739405538125</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09075330589015722</v>
+        <v>0.09079797040122481</v>
       </c>
       <c r="C69">
-        <v>0.6348024918124833</v>
+        <v>0.6107384315448263</v>
       </c>
       <c r="D69">
-        <v>2.009032491812484</v>
+        <v>2.007658431544827</v>
       </c>
       <c r="E69">
-        <v>0.9912300000000002</v>
+        <v>1.01392</v>
       </c>
       <c r="F69">
-        <v>1.52023</v>
+        <v>1.54292</v>
       </c>
       <c r="G69">
         <v>0.146</v>
@@ -6939,28 +6939,28 @@
         <v>0.285</v>
       </c>
       <c r="M69">
-        <v>0.109304537</v>
+        <v>0.110935948</v>
       </c>
       <c r="N69">
-        <v>0.1756954629999999</v>
+        <v>0.1740640519999999</v>
       </c>
       <c r="O69">
-        <v>0.03338213796999999</v>
+        <v>0.03307216987999999</v>
       </c>
       <c r="P69">
-        <v>0.1423133250299999</v>
+        <v>0.14099188212</v>
       </c>
       <c r="Q69">
-        <v>0.2123133250299999</v>
+        <v>0.21099188212</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1567671996671431</v>
+        <v>0.1599857825038276</v>
       </c>
       <c r="T69">
-        <v>2.032403231974587</v>
+        <v>2.091352706948068</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.60739405538125</v>
+        <v>2.569050025155055</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09079797040122481</v>
+        <v>0.09084263491229243</v>
       </c>
       <c r="C70">
-        <v>0.6107384315448263</v>
+        <v>0.5866762495456388</v>
       </c>
       <c r="D70">
-        <v>2.007658431544827</v>
+        <v>2.006286249545639</v>
       </c>
       <c r="E70">
-        <v>1.01392</v>
+        <v>1.03661</v>
       </c>
       <c r="F70">
-        <v>1.54292</v>
+        <v>1.56561</v>
       </c>
       <c r="G70">
         <v>0.146</v>
@@ -7021,28 +7021,28 @@
         <v>0.285</v>
       </c>
       <c r="M70">
-        <v>0.110935948</v>
+        <v>0.112567359</v>
       </c>
       <c r="N70">
-        <v>0.1740640519999999</v>
+        <v>0.1724326409999999</v>
       </c>
       <c r="O70">
-        <v>0.03307216987999999</v>
+        <v>0.03276220178999999</v>
       </c>
       <c r="P70">
-        <v>0.14099188212</v>
+        <v>0.1396704392099999</v>
       </c>
       <c r="Q70">
-        <v>0.21099188212</v>
+        <v>0.2096704392099999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1599857825038276</v>
+        <v>0.1634120158461046</v>
       </c>
       <c r="T70">
-        <v>2.091352706948068</v>
+        <v>2.154105373855322</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.569050025155055</v>
+        <v>2.531817416094837</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09084263491229243</v>
+        <v>0.09309859942336003</v>
       </c>
       <c r="C71">
-        <v>0.5866762495456388</v>
+        <v>0.4970371281512374</v>
       </c>
       <c r="D71">
-        <v>2.006286249545639</v>
+        <v>1.939337128151238</v>
       </c>
       <c r="E71">
-        <v>1.03661</v>
+        <v>1.0593</v>
       </c>
       <c r="F71">
-        <v>1.56561</v>
+        <v>1.5883</v>
       </c>
       <c r="G71">
         <v>0.146</v>
@@ -7103,45 +7103,45 @@
         <v>0.285</v>
       </c>
       <c r="M71">
-        <v>0.112567359</v>
+        <v>0.12039314</v>
       </c>
       <c r="N71">
-        <v>0.1724326409999999</v>
+        <v>0.16460686</v>
       </c>
       <c r="O71">
-        <v>0.03276220178999999</v>
+        <v>0.0312753034</v>
       </c>
       <c r="P71">
-        <v>0.1396704392099999</v>
+        <v>0.1333315566</v>
       </c>
       <c r="Q71">
-        <v>0.2096704392099999</v>
+        <v>0.2033315566</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1634120158461046</v>
+        <v>0.1670666647445334</v>
       </c>
       <c r="T71">
-        <v>2.154105373855322</v>
+        <v>2.221041551889726</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.19</v>
       </c>
       <c r="W71">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.531817416094837</v>
+        <v>2.367244512436505</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09309859942336003</v>
+        <v>0.09317485393442766</v>
       </c>
       <c r="C72">
-        <v>0.4970371281512374</v>
+        <v>0.472162140466805</v>
       </c>
       <c r="D72">
-        <v>1.939337128151238</v>
+        <v>1.937152140466805</v>
       </c>
       <c r="E72">
-        <v>1.0593</v>
+        <v>1.08199</v>
       </c>
       <c r="F72">
-        <v>1.5883</v>
+        <v>1.61099</v>
       </c>
       <c r="G72">
         <v>0.146</v>
@@ -7185,28 +7185,28 @@
         <v>0.285</v>
       </c>
       <c r="M72">
-        <v>0.12039314</v>
+        <v>0.122113042</v>
       </c>
       <c r="N72">
-        <v>0.16460686</v>
+        <v>0.1628869579999999</v>
       </c>
       <c r="O72">
-        <v>0.0312753034</v>
+        <v>0.03094852201999999</v>
       </c>
       <c r="P72">
-        <v>0.1333315566</v>
+        <v>0.13193843598</v>
       </c>
       <c r="Q72">
-        <v>0.2033315566</v>
+        <v>0.20193843598</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1670666647445334</v>
+        <v>0.1709733583945781</v>
       </c>
       <c r="T72">
-        <v>2.221041551889726</v>
+        <v>2.292594018064434</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.367244512436505</v>
+        <v>2.333903040430357</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09317485393442765</v>
+        <v>0.09325110844549525</v>
       </c>
       <c r="C73">
-        <v>0.4721621404668055</v>
+        <v>0.4472920707497172</v>
       </c>
       <c r="D73">
-        <v>1.937152140466806</v>
+        <v>1.934972070749717</v>
       </c>
       <c r="E73">
-        <v>1.08199</v>
+        <v>1.10468</v>
       </c>
       <c r="F73">
-        <v>1.61099</v>
+        <v>1.63368</v>
       </c>
       <c r="G73">
         <v>0.146</v>
@@ -7267,28 +7267,28 @@
         <v>0.285</v>
       </c>
       <c r="M73">
-        <v>0.122113042</v>
+        <v>0.123832944</v>
       </c>
       <c r="N73">
-        <v>0.162886958</v>
+        <v>0.161167056</v>
       </c>
       <c r="O73">
-        <v>0.03094852201999999</v>
+        <v>0.03062174064</v>
       </c>
       <c r="P73">
-        <v>0.13193843598</v>
+        <v>0.13054531536</v>
       </c>
       <c r="Q73">
-        <v>0.20193843598</v>
+        <v>0.20054531536</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1709733583945781</v>
+        <v>0.1751591015910544</v>
       </c>
       <c r="T73">
-        <v>2.292594018064433</v>
+        <v>2.369257374680191</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.333903040430358</v>
+        <v>2.30148772042438</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09325110844549525</v>
+        <v>0.09332736295656285</v>
       </c>
       <c r="C74">
-        <v>0.4472920707497172</v>
+        <v>0.4224269024146057</v>
       </c>
       <c r="D74">
-        <v>1.934972070749717</v>
+        <v>1.932796902414606</v>
       </c>
       <c r="E74">
-        <v>1.10468</v>
+        <v>1.12737</v>
       </c>
       <c r="F74">
-        <v>1.63368</v>
+        <v>1.65637</v>
       </c>
       <c r="G74">
         <v>0.146</v>
@@ -7349,28 +7349,28 @@
         <v>0.285</v>
       </c>
       <c r="M74">
-        <v>0.123832944</v>
+        <v>0.125552846</v>
       </c>
       <c r="N74">
-        <v>0.161167056</v>
+        <v>0.159447154</v>
       </c>
       <c r="O74">
-        <v>0.03062174064</v>
+        <v>0.03029495925999999</v>
       </c>
       <c r="P74">
-        <v>0.13054531536</v>
+        <v>0.1291521947399999</v>
       </c>
       <c r="Q74">
-        <v>0.20054531536</v>
+        <v>0.19915219474</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1751591015910544</v>
+        <v>0.1796548998391217</v>
       </c>
       <c r="T74">
-        <v>2.369257374680191</v>
+        <v>2.451599498452672</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.30148772042438</v>
+        <v>2.269960491377471</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09332736295656285</v>
+        <v>0.09340361746763048</v>
       </c>
       <c r="C75">
-        <v>0.4224269024146057</v>
+        <v>0.3975666189505975</v>
       </c>
       <c r="D75">
-        <v>1.932796902414606</v>
+        <v>1.930626618950597</v>
       </c>
       <c r="E75">
-        <v>1.12737</v>
+        <v>1.15006</v>
       </c>
       <c r="F75">
-        <v>1.65637</v>
+        <v>1.67906</v>
       </c>
       <c r="G75">
         <v>0.146</v>
@@ -7431,28 +7431,28 @@
         <v>0.285</v>
       </c>
       <c r="M75">
-        <v>0.125552846</v>
+        <v>0.127272748</v>
       </c>
       <c r="N75">
-        <v>0.159447154</v>
+        <v>0.157727252</v>
       </c>
       <c r="O75">
-        <v>0.03029495925999999</v>
+        <v>0.02996817787999999</v>
       </c>
       <c r="P75">
-        <v>0.1291521947399999</v>
+        <v>0.12775907412</v>
       </c>
       <c r="Q75">
-        <v>0.19915219474</v>
+        <v>0.19775907412</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1796548998391217</v>
+        <v>0.1844965287216556</v>
       </c>
       <c r="T75">
-        <v>2.451599498452672</v>
+        <v>2.540275631746114</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.269960491377471</v>
+        <v>2.2392853496021</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09340361746763048</v>
+        <v>0.09347987197869809</v>
       </c>
       <c r="C76">
-        <v>0.3975666189505975</v>
+        <v>0.372711203920896</v>
       </c>
       <c r="D76">
-        <v>1.930626618950597</v>
+        <v>1.928461203920896</v>
       </c>
       <c r="E76">
-        <v>1.15006</v>
+        <v>1.17275</v>
       </c>
       <c r="F76">
-        <v>1.67906</v>
+        <v>1.70175</v>
       </c>
       <c r="G76">
         <v>0.146</v>
@@ -7513,28 +7513,28 @@
         <v>0.285</v>
       </c>
       <c r="M76">
-        <v>0.127272748</v>
+        <v>0.12899265</v>
       </c>
       <c r="N76">
-        <v>0.157727252</v>
+        <v>0.15600735</v>
       </c>
       <c r="O76">
-        <v>0.02996817787999999</v>
+        <v>0.02964139649999999</v>
       </c>
       <c r="P76">
-        <v>0.12775907412</v>
+        <v>0.1263659535</v>
       </c>
       <c r="Q76">
-        <v>0.19775907412</v>
+        <v>0.1963659535</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1844965287216556</v>
+        <v>0.1897254879147923</v>
       </c>
       <c r="T76">
-        <v>2.540275631746114</v>
+        <v>2.63604585570303</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.2392853496021</v>
+        <v>2.209428211607405</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09347987197869809</v>
+        <v>0.09355612648976569</v>
       </c>
       <c r="C77">
-        <v>0.372711203920896</v>
+        <v>0.3478606409623619</v>
       </c>
       <c r="D77">
-        <v>1.928461203920896</v>
+        <v>1.926300640962362</v>
       </c>
       <c r="E77">
-        <v>1.17275</v>
+        <v>1.19544</v>
       </c>
       <c r="F77">
-        <v>1.70175</v>
+        <v>1.72444</v>
       </c>
       <c r="G77">
         <v>0.146</v>
@@ -7595,28 +7595,28 @@
         <v>0.285</v>
       </c>
       <c r="M77">
-        <v>0.12899265</v>
+        <v>0.130712552</v>
       </c>
       <c r="N77">
-        <v>0.15600735</v>
+        <v>0.1542874479999999</v>
       </c>
       <c r="O77">
-        <v>0.02964139649999999</v>
+        <v>0.02931461511999999</v>
       </c>
       <c r="P77">
-        <v>0.1263659535</v>
+        <v>0.12497283288</v>
       </c>
       <c r="Q77">
-        <v>0.1963659535</v>
+        <v>0.1949728328799999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1897254879147923</v>
+        <v>0.195390193707357</v>
       </c>
       <c r="T77">
-        <v>2.63604585570303</v>
+        <v>2.739796931656357</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.209428211607405</v>
+        <v>2.180356787770465</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09355612648976569</v>
+        <v>0.09363238100083329</v>
       </c>
       <c r="C78">
-        <v>0.3478606409623619</v>
+        <v>0.3230149137851066</v>
       </c>
       <c r="D78">
-        <v>1.926300640962362</v>
+        <v>1.924144913785107</v>
       </c>
       <c r="E78">
-        <v>1.19544</v>
+        <v>1.21813</v>
       </c>
       <c r="F78">
-        <v>1.72444</v>
+        <v>1.74713</v>
       </c>
       <c r="G78">
         <v>0.146</v>
@@ -7677,28 +7677,28 @@
         <v>0.285</v>
       </c>
       <c r="M78">
-        <v>0.130712552</v>
+        <v>0.132432454</v>
       </c>
       <c r="N78">
-        <v>0.1542874479999999</v>
+        <v>0.152567546</v>
       </c>
       <c r="O78">
-        <v>0.02931461511999999</v>
+        <v>0.02898783374</v>
       </c>
       <c r="P78">
-        <v>0.12497283288</v>
+        <v>0.12357971226</v>
       </c>
       <c r="Q78">
-        <v>0.1949728328799999</v>
+        <v>0.19357971226</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.195390193707357</v>
+        <v>0.2015474826123187</v>
       </c>
       <c r="T78">
-        <v>2.739796931656357</v>
+        <v>2.852569840301277</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.180356787770465</v>
+        <v>2.152040465851369</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09363238100083329</v>
+        <v>0.0937086355119009</v>
       </c>
       <c r="C79">
-        <v>0.3230149137851066</v>
+        <v>0.2981740061720779</v>
       </c>
       <c r="D79">
-        <v>1.924144913785107</v>
+        <v>1.921994006172078</v>
       </c>
       <c r="E79">
-        <v>1.21813</v>
+        <v>1.24082</v>
       </c>
       <c r="F79">
-        <v>1.74713</v>
+        <v>1.76982</v>
       </c>
       <c r="G79">
         <v>0.146</v>
@@ -7759,28 +7759,28 @@
         <v>0.285</v>
       </c>
       <c r="M79">
-        <v>0.132432454</v>
+        <v>0.134152356</v>
       </c>
       <c r="N79">
-        <v>0.152567546</v>
+        <v>0.1508476439999999</v>
       </c>
       <c r="O79">
-        <v>0.02898783374</v>
+        <v>0.02866105235999999</v>
       </c>
       <c r="P79">
-        <v>0.12357971226</v>
+        <v>0.12218659164</v>
       </c>
       <c r="Q79">
-        <v>0.19357971226</v>
+        <v>0.19218659164</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2015474826123187</v>
+        <v>0.208264525054095</v>
       </c>
       <c r="T79">
-        <v>2.852569840301277</v>
+        <v>2.97559483155028</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.152040465851369</v>
+        <v>2.124450203468658</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0937086355119009</v>
+        <v>0.09378489002296851</v>
       </c>
       <c r="C80">
-        <v>0.2981740061720779</v>
+        <v>0.273337901978657</v>
       </c>
       <c r="D80">
-        <v>1.921994006172078</v>
+        <v>1.919847901978657</v>
       </c>
       <c r="E80">
-        <v>1.24082</v>
+        <v>1.26351</v>
       </c>
       <c r="F80">
-        <v>1.76982</v>
+        <v>1.79251</v>
       </c>
       <c r="G80">
         <v>0.146</v>
@@ -7841,28 +7841,28 @@
         <v>0.285</v>
       </c>
       <c r="M80">
-        <v>0.134152356</v>
+        <v>0.135872258</v>
       </c>
       <c r="N80">
-        <v>0.1508476439999999</v>
+        <v>0.149127742</v>
       </c>
       <c r="O80">
-        <v>0.02866105235999999</v>
+        <v>0.02833427097999999</v>
       </c>
       <c r="P80">
-        <v>0.12218659164</v>
+        <v>0.12079347102</v>
       </c>
       <c r="Q80">
-        <v>0.19218659164</v>
+        <v>0.19079347102</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.208264525054095</v>
+        <v>0.2156212858236596</v>
       </c>
       <c r="T80">
-        <v>2.97559483155028</v>
+        <v>3.110336488632523</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.124450203468658</v>
+        <v>2.097558428741207</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09378489002296851</v>
+        <v>0.09386114453403611</v>
       </c>
       <c r="C81">
-        <v>0.273337901978657</v>
+        <v>0.2485065851322543</v>
       </c>
       <c r="D81">
-        <v>1.919847901978657</v>
+        <v>1.917706585132254</v>
       </c>
       <c r="E81">
-        <v>1.26351</v>
+        <v>1.2862</v>
       </c>
       <c r="F81">
-        <v>1.79251</v>
+        <v>1.8152</v>
       </c>
       <c r="G81">
         <v>0.146</v>
@@ -7923,28 +7923,28 @@
         <v>0.285</v>
       </c>
       <c r="M81">
-        <v>0.135872258</v>
+        <v>0.13759216</v>
       </c>
       <c r="N81">
-        <v>0.149127742</v>
+        <v>0.14740784</v>
       </c>
       <c r="O81">
-        <v>0.02833427097999999</v>
+        <v>0.02800748959999999</v>
       </c>
       <c r="P81">
-        <v>0.12079347102</v>
+        <v>0.1194003504</v>
       </c>
       <c r="Q81">
-        <v>0.19079347102</v>
+        <v>0.1894003504</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2156212858236596</v>
+        <v>0.2237137226701806</v>
       </c>
       <c r="T81">
-        <v>3.110336488632523</v>
+        <v>3.258552311422989</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.097558428741207</v>
+        <v>2.071338948381942</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09386114453403611</v>
+        <v>0.09393739904510373</v>
       </c>
       <c r="C82">
-        <v>0.2485065851322543</v>
+        <v>0.2236800396319039</v>
       </c>
       <c r="D82">
-        <v>1.917706585132254</v>
+        <v>1.915570039631904</v>
       </c>
       <c r="E82">
-        <v>1.2862</v>
+        <v>1.30889</v>
       </c>
       <c r="F82">
-        <v>1.8152</v>
+        <v>1.83789</v>
       </c>
       <c r="G82">
         <v>0.146</v>
@@ -8005,28 +8005,28 @@
         <v>0.285</v>
       </c>
       <c r="M82">
-        <v>0.13759216</v>
+        <v>0.139312062</v>
       </c>
       <c r="N82">
-        <v>0.14740784</v>
+        <v>0.1456879379999999</v>
       </c>
       <c r="O82">
-        <v>0.02800748959999999</v>
+        <v>0.02768070821999999</v>
       </c>
       <c r="P82">
-        <v>0.1194003504</v>
+        <v>0.1180072297799999</v>
       </c>
       <c r="Q82">
-        <v>0.1894003504</v>
+        <v>0.18800722978</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2237137226701806</v>
+        <v>0.2326579949742302</v>
       </c>
       <c r="T82">
-        <v>3.258552311422989</v>
+        <v>3.422369799770347</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.071338948381942</v>
+        <v>2.045766862599449</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09393739904510373</v>
+        <v>0.09401365355617133</v>
       </c>
       <c r="C83">
-        <v>0.2236800396319039</v>
+        <v>0.198858249547871</v>
       </c>
       <c r="D83">
-        <v>1.915570039631904</v>
+        <v>1.913438249547871</v>
       </c>
       <c r="E83">
-        <v>1.30889</v>
+        <v>1.33158</v>
       </c>
       <c r="F83">
-        <v>1.83789</v>
+        <v>1.86058</v>
       </c>
       <c r="G83">
         <v>0.146</v>
@@ -8087,28 +8087,28 @@
         <v>0.285</v>
       </c>
       <c r="M83">
-        <v>0.139312062</v>
+        <v>0.141031964</v>
       </c>
       <c r="N83">
-        <v>0.1456879379999999</v>
+        <v>0.1439680359999999</v>
       </c>
       <c r="O83">
-        <v>0.02768070821999999</v>
+        <v>0.02735392683999999</v>
       </c>
       <c r="P83">
-        <v>0.1180072297799999</v>
+        <v>0.11661410916</v>
       </c>
       <c r="Q83">
-        <v>0.18800722978</v>
+        <v>0.18661410916</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2326579949742302</v>
+        <v>0.242596075312063</v>
       </c>
       <c r="T83">
-        <v>3.422369799770347</v>
+        <v>3.60438923126741</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.045766862599449</v>
+        <v>2.020818486226285</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09401365355617133</v>
+        <v>0.1036365680672389</v>
       </c>
       <c r="C84">
-        <v>0.198858249547871</v>
+        <v>-0.05946138454736283</v>
       </c>
       <c r="D84">
-        <v>1.913438249547871</v>
+        <v>1.677808615452637</v>
       </c>
       <c r="E84">
-        <v>1.33158</v>
+        <v>1.35427</v>
       </c>
       <c r="F84">
-        <v>1.86058</v>
+        <v>1.88327</v>
       </c>
       <c r="G84">
         <v>0.146</v>
@@ -8169,45 +8169,45 @@
         <v>0.285</v>
       </c>
       <c r="M84">
-        <v>0.141031964</v>
+        <v>0.1694943</v>
       </c>
       <c r="N84">
-        <v>0.1439680359999999</v>
+        <v>0.1155057</v>
       </c>
       <c r="O84">
-        <v>0.02735392683999999</v>
+        <v>0.02194608299999999</v>
       </c>
       <c r="P84">
-        <v>0.11661410916</v>
+        <v>0.09355961699999997</v>
       </c>
       <c r="Q84">
-        <v>0.18661410916</v>
+        <v>0.163559617</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.242596075312063</v>
+        <v>0.2537033415719938</v>
       </c>
       <c r="T84">
-        <v>3.60438923126741</v>
+        <v>3.807822713528835</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.19</v>
       </c>
       <c r="W84">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.020818486226285</v>
+        <v>1.681472474295596</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1036365680672389</v>
+        <v>0.1038278425783065</v>
       </c>
       <c r="C85">
-        <v>-0.05946138454736283</v>
+        <v>-0.08624820195347715</v>
       </c>
       <c r="D85">
-        <v>1.677808615452637</v>
+        <v>1.673711798046523</v>
       </c>
       <c r="E85">
-        <v>1.35427</v>
+        <v>1.37696</v>
       </c>
       <c r="F85">
-        <v>1.88327</v>
+        <v>1.90596</v>
       </c>
       <c r="G85">
         <v>0.146</v>
@@ -8251,28 +8251,28 @@
         <v>0.285</v>
       </c>
       <c r="M85">
-        <v>0.1694943</v>
+        <v>0.1715364</v>
       </c>
       <c r="N85">
-        <v>0.1155057</v>
+        <v>0.1134635999999999</v>
       </c>
       <c r="O85">
-        <v>0.02194608299999999</v>
+        <v>0.02155808399999999</v>
       </c>
       <c r="P85">
-        <v>0.09355961699999997</v>
+        <v>0.09190551599999995</v>
       </c>
       <c r="Q85">
-        <v>0.163559617</v>
+        <v>0.161905516</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2537033415719938</v>
+        <v>0.266199016114416</v>
       </c>
       <c r="T85">
-        <v>3.807822713528835</v>
+        <v>4.036685381072937</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.681472474295596</v>
+        <v>1.661454944839695</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1038278425783065</v>
+        <v>0.1040191170893742</v>
       </c>
       <c r="C86">
-        <v>-0.08624820195347693</v>
+        <v>-0.1130150611472793</v>
       </c>
       <c r="D86">
-        <v>1.673711798046523</v>
+        <v>1.669634938852721</v>
       </c>
       <c r="E86">
-        <v>1.37696</v>
+        <v>1.39965</v>
       </c>
       <c r="F86">
-        <v>1.90596</v>
+        <v>1.92865</v>
       </c>
       <c r="G86">
         <v>0.146</v>
@@ -8333,28 +8333,28 @@
         <v>0.285</v>
       </c>
       <c r="M86">
-        <v>0.1715364</v>
+        <v>0.1735785</v>
       </c>
       <c r="N86">
-        <v>0.1134636</v>
+        <v>0.1114215</v>
       </c>
       <c r="O86">
-        <v>0.02155808399999999</v>
+        <v>0.02117008499999999</v>
       </c>
       <c r="P86">
-        <v>0.09190551599999998</v>
+        <v>0.09025141499999999</v>
       </c>
       <c r="Q86">
-        <v>0.161905516</v>
+        <v>0.160251415</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2661990161144158</v>
+        <v>0.2803607805958276</v>
       </c>
       <c r="T86">
-        <v>4.036685381072934</v>
+        <v>4.296063070956251</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.661454944839696</v>
+        <v>1.641908416076876</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1040191170893742</v>
+        <v>0.1042103916004418</v>
       </c>
       <c r="C87">
-        <v>-0.1130150611472793</v>
+        <v>-0.1397621076181692</v>
       </c>
       <c r="D87">
-        <v>1.669634938852721</v>
+        <v>1.665577892381831</v>
       </c>
       <c r="E87">
-        <v>1.39965</v>
+        <v>1.42234</v>
       </c>
       <c r="F87">
-        <v>1.92865</v>
+        <v>1.95134</v>
       </c>
       <c r="G87">
         <v>0.146</v>
@@ -8415,28 +8415,28 @@
         <v>0.285</v>
       </c>
       <c r="M87">
-        <v>0.1735785</v>
+        <v>0.1756206</v>
       </c>
       <c r="N87">
-        <v>0.1114215</v>
+        <v>0.1093794</v>
       </c>
       <c r="O87">
-        <v>0.02117008499999999</v>
+        <v>0.020782086</v>
       </c>
       <c r="P87">
-        <v>0.09025141499999999</v>
+        <v>0.08859731399999998</v>
       </c>
       <c r="Q87">
-        <v>0.160251415</v>
+        <v>0.158597314</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2803607805958276</v>
+        <v>0.2965456542888697</v>
       </c>
       <c r="T87">
-        <v>4.296063070956251</v>
+        <v>4.592494716537183</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.641908416076876</v>
+        <v>1.622816457750401</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1042103916004418</v>
+        <v>0.1044016661115094</v>
       </c>
       <c r="C88">
-        <v>-0.1397621076181692</v>
+        <v>-0.1664894854448742</v>
       </c>
       <c r="D88">
-        <v>1.665577892381831</v>
+        <v>1.661540514555126</v>
       </c>
       <c r="E88">
-        <v>1.42234</v>
+        <v>1.44503</v>
       </c>
       <c r="F88">
-        <v>1.95134</v>
+        <v>1.97403</v>
       </c>
       <c r="G88">
         <v>0.146</v>
@@ -8497,28 +8497,28 @@
         <v>0.285</v>
       </c>
       <c r="M88">
-        <v>0.1756206</v>
+        <v>0.1776627</v>
       </c>
       <c r="N88">
-        <v>0.1093794</v>
+        <v>0.1073373</v>
       </c>
       <c r="O88">
-        <v>0.020782086</v>
+        <v>0.02039408699999999</v>
       </c>
       <c r="P88">
-        <v>0.08859731399999998</v>
+        <v>0.08694321299999998</v>
       </c>
       <c r="Q88">
-        <v>0.158597314</v>
+        <v>0.156943213</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2965456542888697</v>
+        <v>0.315220508550072</v>
       </c>
       <c r="T88">
-        <v>4.592494716537183</v>
+        <v>4.934531230669028</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.622816457750401</v>
+        <v>1.604163395017637</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1044016661115094</v>
+        <v>0.104592940622577</v>
       </c>
       <c r="C89">
-        <v>-0.1664894854448742</v>
+        <v>-0.1931973373125078</v>
       </c>
       <c r="D89">
-        <v>1.661540514555126</v>
+        <v>1.657522662687492</v>
       </c>
       <c r="E89">
-        <v>1.44503</v>
+        <v>1.46772</v>
       </c>
       <c r="F89">
-        <v>1.97403</v>
+        <v>1.99672</v>
       </c>
       <c r="G89">
         <v>0.146</v>
@@ -8579,28 +8579,28 @@
         <v>0.285</v>
       </c>
       <c r="M89">
-        <v>0.1776627</v>
+        <v>0.1797048</v>
       </c>
       <c r="N89">
-        <v>0.1073373</v>
+        <v>0.1052952</v>
       </c>
       <c r="O89">
-        <v>0.02039408699999999</v>
+        <v>0.02000608799999999</v>
       </c>
       <c r="P89">
-        <v>0.08694321299999998</v>
+        <v>0.08528911199999999</v>
       </c>
       <c r="Q89">
-        <v>0.156943213</v>
+        <v>0.155289112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.315220508550072</v>
+        <v>0.3370078385214748</v>
       </c>
       <c r="T89">
-        <v>4.934531230669028</v>
+        <v>5.333573830489514</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.604163395017637</v>
+        <v>1.5859342655288</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.104592940622577</v>
+        <v>0.1047842151336446</v>
       </c>
       <c r="C90">
-        <v>-0.1931973373125078</v>
+        <v>-0.2198858045293772</v>
       </c>
       <c r="D90">
-        <v>1.657522662687492</v>
+        <v>1.653524195470623</v>
       </c>
       <c r="E90">
-        <v>1.46772</v>
+        <v>1.49041</v>
       </c>
       <c r="F90">
-        <v>1.99672</v>
+        <v>2.01941</v>
       </c>
       <c r="G90">
         <v>0.146</v>
@@ -8661,28 +8661,28 @@
         <v>0.285</v>
       </c>
       <c r="M90">
-        <v>0.1797048</v>
+        <v>0.1817469</v>
       </c>
       <c r="N90">
-        <v>0.1052952</v>
+        <v>0.1032531</v>
       </c>
       <c r="O90">
-        <v>0.02000608799999999</v>
+        <v>0.01961808899999999</v>
       </c>
       <c r="P90">
-        <v>0.08528911199999999</v>
+        <v>0.08363501099999997</v>
       </c>
       <c r="Q90">
-        <v>0.155289112</v>
+        <v>0.153635011</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3370078385214748</v>
+        <v>0.3627565012149507</v>
       </c>
       <c r="T90">
-        <v>5.333573830489514</v>
+        <v>5.80516963027736</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.5859342655288</v>
+        <v>1.568114779399263</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1047842151336446</v>
+        <v>0.1049754896447122</v>
       </c>
       <c r="C91">
-        <v>-0.2198858045293772</v>
+        <v>-0.2465550270435501</v>
       </c>
       <c r="D91">
-        <v>1.653524195470623</v>
+        <v>1.64954497295645</v>
       </c>
       <c r="E91">
-        <v>1.49041</v>
+        <v>1.5131</v>
       </c>
       <c r="F91">
-        <v>2.01941</v>
+        <v>2.0421</v>
       </c>
       <c r="G91">
         <v>0.146</v>
@@ -8743,28 +8743,28 @@
         <v>0.285</v>
       </c>
       <c r="M91">
-        <v>0.1817469</v>
+        <v>0.183789</v>
       </c>
       <c r="N91">
-        <v>0.1032531</v>
+        <v>0.101211</v>
       </c>
       <c r="O91">
-        <v>0.01961808899999999</v>
+        <v>0.01923008999999999</v>
       </c>
       <c r="P91">
-        <v>0.08363501099999997</v>
+        <v>0.08198090999999998</v>
       </c>
       <c r="Q91">
-        <v>0.153635011</v>
+        <v>0.15198091</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3627565012149507</v>
+        <v>0.393654896447122</v>
       </c>
       <c r="T91">
-        <v>5.80516963027736</v>
+        <v>6.371084590022778</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.568114779399263</v>
+        <v>1.550691281850383</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1049754896447122</v>
+        <v>0.1051667641557798</v>
       </c>
       <c r="C92">
-        <v>-0.2465550270435501</v>
+        <v>-0.2732051434591833</v>
       </c>
       <c r="D92">
-        <v>1.64954497295645</v>
+        <v>1.645584856540817</v>
       </c>
       <c r="E92">
-        <v>1.5131</v>
+        <v>1.53579</v>
       </c>
       <c r="F92">
-        <v>2.0421</v>
+        <v>2.06479</v>
       </c>
       <c r="G92">
         <v>0.146</v>
@@ -8825,28 +8825,28 @@
         <v>0.285</v>
       </c>
       <c r="M92">
-        <v>0.183789</v>
+        <v>0.1858311</v>
       </c>
       <c r="N92">
-        <v>0.101211</v>
+        <v>0.09916889999999995</v>
       </c>
       <c r="O92">
-        <v>0.01923008999999999</v>
+        <v>0.01884209099999999</v>
       </c>
       <c r="P92">
-        <v>0.08198090999999998</v>
+        <v>0.08032680899999996</v>
       </c>
       <c r="Q92">
-        <v>0.15198091</v>
+        <v>0.150326809</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.393654896447122</v>
+        <v>0.4314196017308867</v>
       </c>
       <c r="T92">
-        <v>6.371084590022778</v>
+        <v>7.06275842971162</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.550691281850383</v>
+        <v>1.533650718313565</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1051667641557798</v>
+        <v>0.1053580386668474</v>
       </c>
       <c r="C93">
-        <v>-0.2732051434591833</v>
+        <v>-0.2998362910526136</v>
       </c>
       <c r="D93">
-        <v>1.645584856540817</v>
+        <v>1.641643708947387</v>
       </c>
       <c r="E93">
-        <v>1.53579</v>
+        <v>1.55848</v>
       </c>
       <c r="F93">
-        <v>2.06479</v>
+        <v>2.08748</v>
       </c>
       <c r="G93">
         <v>0.146</v>
@@ -8907,28 +8907,28 @@
         <v>0.285</v>
       </c>
       <c r="M93">
-        <v>0.1858311</v>
+        <v>0.1878732</v>
       </c>
       <c r="N93">
-        <v>0.09916889999999995</v>
+        <v>0.09712679999999996</v>
       </c>
       <c r="O93">
-        <v>0.01884209099999999</v>
+        <v>0.01845409199999999</v>
       </c>
       <c r="P93">
-        <v>0.08032680899999996</v>
+        <v>0.07867270799999997</v>
       </c>
       <c r="Q93">
-        <v>0.150326809</v>
+        <v>0.148672708</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4314196017308867</v>
+        <v>0.4786254833355928</v>
       </c>
       <c r="T93">
-        <v>7.06275842971162</v>
+        <v>7.927350729322675</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.533650718313565</v>
+        <v>1.516980601810157</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1053580386668474</v>
+        <v>0.105549313177915</v>
       </c>
       <c r="C94">
-        <v>-0.2998362910526136</v>
+        <v>-0.3264486057882243</v>
       </c>
       <c r="D94">
-        <v>1.641643708947387</v>
+        <v>1.637721394211776</v>
       </c>
       <c r="E94">
-        <v>1.55848</v>
+        <v>1.58117</v>
       </c>
       <c r="F94">
-        <v>2.08748</v>
+        <v>2.11017</v>
       </c>
       <c r="G94">
         <v>0.146</v>
@@ -8989,28 +8989,28 @@
         <v>0.285</v>
       </c>
       <c r="M94">
-        <v>0.1878732</v>
+        <v>0.1899153</v>
       </c>
       <c r="N94">
-        <v>0.09712679999999996</v>
+        <v>0.09508469999999997</v>
       </c>
       <c r="O94">
-        <v>0.01845409199999999</v>
+        <v>0.01806609299999999</v>
       </c>
       <c r="P94">
-        <v>0.07867270799999997</v>
+        <v>0.07701860699999998</v>
       </c>
       <c r="Q94">
-        <v>0.148672708</v>
+        <v>0.147018607</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4786254833355928</v>
+        <v>0.5393187596845005</v>
       </c>
       <c r="T94">
-        <v>7.927350729322675</v>
+        <v>9.038969400251172</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.516980601810157</v>
+        <v>1.500668982435854</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.105549313177915</v>
+        <v>0.1520141194320357</v>
       </c>
       <c r="C95">
-        <v>-0.3264486057882243</v>
+        <v>-0.9505925872228851</v>
       </c>
       <c r="D95">
-        <v>1.637721394211776</v>
+        <v>1.036267412777115</v>
       </c>
       <c r="E95">
-        <v>1.58117</v>
+        <v>1.603860000000001</v>
       </c>
       <c r="F95">
-        <v>2.11017</v>
+        <v>2.13286</v>
       </c>
       <c r="G95">
         <v>0.146</v>
@@ -9071,45 +9071,45 @@
         <v>0.285</v>
       </c>
       <c r="M95">
-        <v>0.1899153</v>
+        <v>0.3131038480000001</v>
       </c>
       <c r="N95">
-        <v>0.09508469999999997</v>
+        <v>-0.0281038480000001</v>
       </c>
       <c r="O95">
-        <v>0.01806609299999999</v>
+        <v>-0.005339731120000019</v>
       </c>
       <c r="P95">
-        <v>0.07701860699999998</v>
+        <v>-0.02276411688000008</v>
       </c>
       <c r="Q95">
-        <v>0.147018607</v>
+        <v>0.04723588311999993</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5393187596845005</v>
+        <v>0.6314543043285524</v>
       </c>
       <c r="T95">
-        <v>9.038969400251172</v>
+        <v>10.72646425707377</v>
       </c>
       <c r="U95">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.19</v>
+        <v>0.1729458144506738</v>
       </c>
       <c r="W95">
-        <v>0.07290000000000001</v>
+        <v>0.1214115544386411</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.500668982435854</v>
+        <v>0.910241128687757</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1520141194320357</v>
+        <v>0.1530241194320357</v>
       </c>
       <c r="C96">
-        <v>-0.9505925872228851</v>
+        <v>-0.981489471507156</v>
       </c>
       <c r="D96">
-        <v>1.036267412777115</v>
+        <v>1.028060528492844</v>
       </c>
       <c r="E96">
-        <v>1.603860000000001</v>
+        <v>1.62655</v>
       </c>
       <c r="F96">
-        <v>2.13286</v>
+        <v>2.15555</v>
       </c>
       <c r="G96">
         <v>0.146</v>
@@ -9153,37 +9153,37 @@
         <v>0.285</v>
       </c>
       <c r="M96">
-        <v>0.3131038480000001</v>
+        <v>0.31643474</v>
       </c>
       <c r="N96">
-        <v>-0.0281038480000001</v>
+        <v>-0.03143474000000007</v>
       </c>
       <c r="O96">
-        <v>-0.005339731120000019</v>
+        <v>-0.005972600600000014</v>
       </c>
       <c r="P96">
-        <v>-0.02276411688000008</v>
+        <v>-0.02546213940000006</v>
       </c>
       <c r="Q96">
-        <v>0.04723588311999993</v>
+        <v>0.04453786059999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6314543043285524</v>
+        <v>0.7485851651942631</v>
       </c>
       <c r="T96">
-        <v>10.72646425707377</v>
+        <v>12.87175710848853</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1729458144506738</v>
+        <v>0.1711253321932983</v>
       </c>
       <c r="W96">
-        <v>0.1214115544386411</v>
+        <v>0.1216788012340238</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.910241128687757</v>
+        <v>0.9006596431226228</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1530241194320357</v>
+        <v>0.1540341194320357</v>
       </c>
       <c r="C97">
-        <v>-0.981489471507156</v>
+        <v>-1.012257385744304</v>
       </c>
       <c r="D97">
-        <v>1.028060528492844</v>
+        <v>1.019982614255696</v>
       </c>
       <c r="E97">
-        <v>1.62655</v>
+        <v>1.64924</v>
       </c>
       <c r="F97">
-        <v>2.15555</v>
+        <v>2.17824</v>
       </c>
       <c r="G97">
         <v>0.146</v>
@@ -9235,37 +9235,37 @@
         <v>0.285</v>
       </c>
       <c r="M97">
-        <v>0.31643474</v>
+        <v>0.3197656320000001</v>
       </c>
       <c r="N97">
-        <v>-0.03143474000000007</v>
+        <v>-0.0347656320000001</v>
       </c>
       <c r="O97">
-        <v>-0.005972600600000014</v>
+        <v>-0.006605470080000019</v>
       </c>
       <c r="P97">
-        <v>-0.02546213940000006</v>
+        <v>-0.02816016192000008</v>
       </c>
       <c r="Q97">
-        <v>0.04453786059999995</v>
+        <v>0.04183983807999993</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7485851651942631</v>
+        <v>0.9242814564928293</v>
       </c>
       <c r="T97">
-        <v>12.87175710848853</v>
+        <v>16.08969638561067</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1711253321932983</v>
+        <v>0.1693427766496181</v>
       </c>
       <c r="W97">
-        <v>0.1216788012340238</v>
+        <v>0.1219404803878361</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9006596431226228</v>
+        <v>0.8912777718400954</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1540341194320357</v>
+        <v>0.1550441194320357</v>
       </c>
       <c r="C98">
-        <v>-1.012257385744304</v>
+        <v>-1.04289934635261</v>
       </c>
       <c r="D98">
-        <v>1.019982614255696</v>
+        <v>1.012030653647391</v>
       </c>
       <c r="E98">
-        <v>1.64924</v>
+        <v>1.67193</v>
       </c>
       <c r="F98">
-        <v>2.17824</v>
+        <v>2.20093</v>
       </c>
       <c r="G98">
         <v>0.146</v>
@@ -9317,37 +9317,37 @@
         <v>0.285</v>
       </c>
       <c r="M98">
-        <v>0.3197656320000001</v>
+        <v>0.3230965240000001</v>
       </c>
       <c r="N98">
-        <v>-0.0347656320000001</v>
+        <v>-0.03809652400000008</v>
       </c>
       <c r="O98">
-        <v>-0.006605470080000019</v>
+        <v>-0.007238339560000014</v>
       </c>
       <c r="P98">
-        <v>-0.02816016192000008</v>
+        <v>-0.03085818444000006</v>
       </c>
       <c r="Q98">
-        <v>0.04183983807999993</v>
+        <v>0.03914181555999995</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.924281456492827</v>
+        <v>1.217108608657103</v>
       </c>
       <c r="T98">
-        <v>16.08969638561062</v>
+        <v>21.4529285141475</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1693427766496181</v>
+        <v>0.167596974828488</v>
       </c>
       <c r="W98">
-        <v>0.1219404803878361</v>
+        <v>0.122196764095178</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8912777718400954</v>
+        <v>0.8820893412025688</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1550441194320357</v>
+        <v>0.1560541194320357</v>
       </c>
       <c r="C99">
-        <v>-1.04289934635261</v>
+        <v>-1.073418276411962</v>
       </c>
       <c r="D99">
-        <v>1.012030653647391</v>
+        <v>1.004201723588038</v>
       </c>
       <c r="E99">
-        <v>1.67193</v>
+        <v>1.69462</v>
       </c>
       <c r="F99">
-        <v>2.20093</v>
+        <v>2.22362</v>
       </c>
       <c r="G99">
         <v>0.146</v>
@@ -9399,37 +9399,37 @@
         <v>0.285</v>
       </c>
       <c r="M99">
-        <v>0.3230965240000001</v>
+        <v>0.326427416</v>
       </c>
       <c r="N99">
-        <v>-0.03809652400000008</v>
+        <v>-0.04142741600000005</v>
       </c>
       <c r="O99">
-        <v>-0.007238339560000014</v>
+        <v>-0.007871209040000009</v>
       </c>
       <c r="P99">
-        <v>-0.03085818444000006</v>
+        <v>-0.03355620696000004</v>
       </c>
       <c r="Q99">
-        <v>0.03914181555999995</v>
+        <v>0.03644379303999996</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.217108608657103</v>
+        <v>1.802762912985654</v>
       </c>
       <c r="T99">
-        <v>21.4529285141475</v>
+        <v>32.17939277122125</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.167596974828488</v>
+        <v>0.1658868016159525</v>
       </c>
       <c r="W99">
-        <v>0.122196764095178</v>
+        <v>0.1224478175227782</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8820893412025688</v>
+        <v>0.8730884295576447</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1560541194320357</v>
+        <v>0.1570641194320357</v>
       </c>
       <c r="C100">
-        <v>-1.073418276411962</v>
+        <v>-1.103817009246417</v>
       </c>
       <c r="D100">
-        <v>1.004201723588038</v>
+        <v>0.9964929907535832</v>
       </c>
       <c r="E100">
-        <v>1.69462</v>
+        <v>1.71731</v>
       </c>
       <c r="F100">
-        <v>2.22362</v>
+        <v>2.24631</v>
       </c>
       <c r="G100">
         <v>0.146</v>
@@ -9481,37 +9481,37 @@
         <v>0.285</v>
       </c>
       <c r="M100">
-        <v>0.326427416</v>
+        <v>0.3297583080000001</v>
       </c>
       <c r="N100">
-        <v>-0.04142741600000005</v>
+        <v>-0.04475830800000008</v>
       </c>
       <c r="O100">
-        <v>-0.007871209040000009</v>
+        <v>-0.008504078520000015</v>
       </c>
       <c r="P100">
-        <v>-0.03355620696000004</v>
+        <v>-0.03625422948000007</v>
       </c>
       <c r="Q100">
-        <v>0.03644379303999996</v>
+        <v>0.03374577051999994</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.802762912985654</v>
+        <v>3.559725825971308</v>
       </c>
       <c r="T100">
-        <v>32.17939277122125</v>
+        <v>64.35878554244249</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1658868016159525</v>
+        <v>0.1642111773572055</v>
       </c>
       <c r="W100">
-        <v>0.1224478175227782</v>
+        <v>0.1226937991639623</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8730884295576447</v>
+        <v>0.8642693545116077</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1570641194320357</v>
-      </c>
-      <c r="C101">
-        <v>-1.103817009246417</v>
-      </c>
-      <c r="D101">
-        <v>0.9964929907535832</v>
-      </c>
-      <c r="E101">
-        <v>1.71731</v>
-      </c>
-      <c r="F101">
-        <v>2.24631</v>
-      </c>
-      <c r="G101">
-        <v>0.146</v>
-      </c>
-      <c r="H101">
-        <v>1.74</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.355</v>
-      </c>
-      <c r="K101">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.285</v>
-      </c>
-      <c r="M101">
-        <v>0.3297583080000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.04475830800000008</v>
-      </c>
-      <c r="O101">
-        <v>-0.008504078520000015</v>
-      </c>
-      <c r="P101">
-        <v>-0.03625422948000007</v>
-      </c>
-      <c r="Q101">
-        <v>0.03374577051999994</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.559725825971308</v>
-      </c>
-      <c r="T101">
-        <v>64.35878554244249</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1642111773572055</v>
-      </c>
-      <c r="W101">
-        <v>0.1226937991639623</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8642693545116077</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
